--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -1739,10 +1739,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118658920</v>
+        <v>118659699</v>
       </c>
       <c r="B11" t="n">
-        <v>104940</v>
+        <v>89954</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1755,27 +1755,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>4189</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1783,10 +1790,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585085</v>
+        <v>585361</v>
       </c>
       <c r="R11" t="n">
-        <v>6558588</v>
+        <v>6558542</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1819,11 +1826,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Liten lokal med en blommande stjälk.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,10 +1853,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118659699</v>
+        <v>118658920</v>
       </c>
       <c r="B12" t="n">
-        <v>89954</v>
+        <v>104940</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,34 +1869,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4189</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1902,10 +1897,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585361</v>
+        <v>585085</v>
       </c>
       <c r="R12" t="n">
-        <v>6558542</v>
+        <v>6558588</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1938,6 +1933,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Liten lokal med en blommande stjälk.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118526068</v>
+        <v>118525987</v>
       </c>
       <c r="B2" t="n">
-        <v>8416</v>
+        <v>91124</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,36 +691,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -728,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585130</v>
+        <v>585152</v>
       </c>
       <c r="R2" t="n">
-        <v>6558822</v>
+        <v>6558846</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -773,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118525987</v>
+        <v>118526068</v>
       </c>
       <c r="B3" t="n">
-        <v>91124</v>
+        <v>8416</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,30 +810,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585152</v>
+        <v>585130</v>
       </c>
       <c r="R3" t="n">
-        <v>6558846</v>
+        <v>6558822</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118658795</v>
+        <v>118659687</v>
       </c>
       <c r="B4" t="n">
-        <v>94466</v>
+        <v>89954</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>4189</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -959,11 +959,10 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -971,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585109</v>
+        <v>585362</v>
       </c>
       <c r="R4" t="n">
-        <v>6558533</v>
+        <v>6558555</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,7 +1010,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Vid roten på gammal granlåga. Rikligt med torrgranar som angripits av granbarkborrar. Gott om granlågor av både gamla rötskadade och färska torrgranar.</t>
+          <t>Fjolårsexemplar i barrmatta under gammal gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118659096</v>
+        <v>118659699</v>
       </c>
       <c r="B5" t="n">
-        <v>94466</v>
+        <v>89954</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,35 +1054,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>4189</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1091,10 +1089,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585101</v>
+        <v>585361</v>
       </c>
       <c r="R5" t="n">
-        <v>6558610</v>
+        <v>6558542</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1127,11 +1125,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På kraftigt rötangripen granstubbe.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118659687</v>
+        <v>118658920</v>
       </c>
       <c r="B6" t="n">
-        <v>89954</v>
+        <v>104940</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,34 +1168,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4189</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1210,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585362</v>
+        <v>585085</v>
       </c>
       <c r="R6" t="n">
-        <v>6558555</v>
+        <v>6558588</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1250,7 +1236,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Fjolårsexemplar i barrmatta under gammal gran.</t>
+          <t>Liten lokal med en blommande stjälk.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,7 +1264,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118659613</v>
+        <v>118659096</v>
       </c>
       <c r="B7" t="n">
         <v>94466</v>
@@ -1313,7 +1299,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1330,10 +1316,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585340</v>
+        <v>585101</v>
       </c>
       <c r="R7" t="n">
-        <v>6558598</v>
+        <v>6558610</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1370,7 +1356,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Vid roten på gammal kraftigt rötskadad granlåga.</t>
+          <t>På kraftigt rötangripen granstubbe.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1398,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118659200</v>
+        <v>118659444</v>
       </c>
       <c r="B8" t="n">
-        <v>90504</v>
+        <v>91124</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1410,25 +1396,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1441,10 +1427,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585124</v>
+        <v>585230</v>
       </c>
       <c r="R8" t="n">
-        <v>6558615</v>
+        <v>6558800</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1481,7 +1467,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På granlåga. Gott om död ved i form av torrträd och lågor av gran.</t>
+          <t>På högstubbe av gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,10 +1495,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118659661</v>
+        <v>118659200</v>
       </c>
       <c r="B9" t="n">
-        <v>89957</v>
+        <v>90504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,33 +1511,25 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2008</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1560,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585347</v>
+        <v>585124</v>
       </c>
       <c r="R9" t="n">
-        <v>6558564</v>
+        <v>6558615</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1600,7 +1578,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>8 fjolårsexemplar i barrmatta under gammal gran.</t>
+          <t>På granlåga. Gott om död ved i form av torrträd och lågor av gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118659444</v>
+        <v>118658795</v>
       </c>
       <c r="B10" t="n">
-        <v>91124</v>
+        <v>94466</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1644,26 +1622,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1339</v>
+        <v>210</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1671,10 +1658,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585230</v>
+        <v>585109</v>
       </c>
       <c r="R10" t="n">
-        <v>6558800</v>
+        <v>6558533</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1711,7 +1698,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På högstubbe av gran.</t>
+          <t>Vid roten på gammal granlåga. Rikligt med torrgranar som angripits av granbarkborrar. Gott om granlågor av både gamla rötskadade och färska torrgranar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1739,10 +1726,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118659699</v>
+        <v>118659661</v>
       </c>
       <c r="B11" t="n">
-        <v>89954</v>
+        <v>89957</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1751,20 +1738,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4189</v>
+        <v>2008</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1774,7 +1761,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1790,10 +1777,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585361</v>
+        <v>585347</v>
       </c>
       <c r="R11" t="n">
-        <v>6558542</v>
+        <v>6558564</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1826,6 +1813,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>8 fjolårsexemplar i barrmatta under gammal gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1853,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118658920</v>
+        <v>118659613</v>
       </c>
       <c r="B12" t="n">
-        <v>104940</v>
+        <v>94466</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1869,25 +1861,33 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585085</v>
+        <v>585340</v>
       </c>
       <c r="R12" t="n">
-        <v>6558588</v>
+        <v>6558598</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Liten lokal med en blommande stjälk.</t>
+          <t>Vid roten på gammal kraftigt rötskadad granlåga.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -1264,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118659096</v>
+        <v>118659444</v>
       </c>
       <c r="B7" t="n">
-        <v>94466</v>
+        <v>91124</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,35 +1280,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>1339</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1316,10 +1307,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585101</v>
+        <v>585230</v>
       </c>
       <c r="R7" t="n">
-        <v>6558610</v>
+        <v>6558800</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1356,7 +1347,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På kraftigt rötangripen granstubbe.</t>
+          <t>På högstubbe av gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118659444</v>
+        <v>118659200</v>
       </c>
       <c r="B8" t="n">
-        <v>91124</v>
+        <v>90504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,25 +1387,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1427,10 +1418,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585230</v>
+        <v>585124</v>
       </c>
       <c r="R8" t="n">
-        <v>6558800</v>
+        <v>6558615</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1467,7 +1458,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På högstubbe av gran.</t>
+          <t>På granlåga. Gott om död ved i form av torrträd och lågor av gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118659200</v>
+        <v>118659096</v>
       </c>
       <c r="B9" t="n">
-        <v>90504</v>
+        <v>94466</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,30 +1498,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585124</v>
+        <v>585101</v>
       </c>
       <c r="R9" t="n">
-        <v>6558615</v>
+        <v>6558610</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På granlåga. Gott om död ved i form av torrträd och lågor av gran.</t>
+          <t>På kraftigt rötangripen granstubbe.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118525987</v>
+        <v>118526068</v>
       </c>
       <c r="B2" t="n">
-        <v>91124</v>
+        <v>8416</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +728,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585152</v>
+        <v>585130</v>
       </c>
       <c r="R2" t="n">
-        <v>6558846</v>
+        <v>6558822</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +763,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +773,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118526068</v>
+        <v>118525987</v>
       </c>
       <c r="B3" t="n">
-        <v>8416</v>
+        <v>91124</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,36 +816,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585130</v>
+        <v>585152</v>
       </c>
       <c r="R3" t="n">
-        <v>6558822</v>
+        <v>6558846</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118659687</v>
+        <v>118659699</v>
       </c>
       <c r="B4" t="n">
         <v>89954</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585362</v>
+        <v>585361</v>
       </c>
       <c r="R4" t="n">
-        <v>6558555</v>
+        <v>6558542</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1006,11 +1006,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fjolårsexemplar i barrmatta under gammal gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1033,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118659699</v>
+        <v>118659687</v>
       </c>
       <c r="B5" t="n">
         <v>89954</v>
@@ -1073,7 +1068,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1089,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585361</v>
+        <v>585362</v>
       </c>
       <c r="R5" t="n">
-        <v>6558542</v>
+        <v>6558555</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1125,6 +1120,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fjolårsexemplar i barrmatta under gammal gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson, Rolf Olsson, Björn Rösch</t>
+          <t>Björn Rösch, Rolf Olsson, Bo Karlsson, Bo Törnquist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118659444</v>
+        <v>118659200</v>
       </c>
       <c r="B7" t="n">
-        <v>91124</v>
+        <v>90504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,25 +1276,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585230</v>
+        <v>585124</v>
       </c>
       <c r="R7" t="n">
-        <v>6558800</v>
+        <v>6558615</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På högstubbe av gran.</t>
+          <t>På granlåga. Gott om död ved i form av torrträd och lågor av gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118659200</v>
+        <v>118658795</v>
       </c>
       <c r="B8" t="n">
-        <v>90504</v>
+        <v>94466</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,30 +1387,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1418,10 +1427,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585124</v>
+        <v>585109</v>
       </c>
       <c r="R8" t="n">
-        <v>6558615</v>
+        <v>6558533</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1458,7 +1467,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På granlåga. Gott om död ved i form av torrträd och lågor av gran.</t>
+          <t>Vid roten på gammal granlåga. Rikligt med torrgranar som angripits av granbarkborrar. Gott om granlågor av både gamla rötskadade och färska torrgranar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1606,10 +1615,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118658795</v>
+        <v>118659444</v>
       </c>
       <c r="B10" t="n">
-        <v>94466</v>
+        <v>91124</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,35 +1631,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>210</v>
+        <v>1339</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585109</v>
+        <v>585230</v>
       </c>
       <c r="R10" t="n">
-        <v>6558533</v>
+        <v>6558800</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Vid roten på gammal granlåga. Rikligt med torrgranar som angripits av granbarkborrar. Gott om granlågor av både gamla rötskadade och färska torrgranar.</t>
+          <t>På högstubbe av gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1726,10 +1726,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118659661</v>
+        <v>118659613</v>
       </c>
       <c r="B11" t="n">
-        <v>89957</v>
+        <v>94466</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,38 +1738,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2008</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1777,10 +1778,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585347</v>
+        <v>585340</v>
       </c>
       <c r="R11" t="n">
-        <v>6558564</v>
+        <v>6558598</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1817,7 +1818,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>8 fjolårsexemplar i barrmatta under gammal gran.</t>
+          <t>Vid roten på gammal kraftigt rötskadad granlåga.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,10 +1846,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118659613</v>
+        <v>118659661</v>
       </c>
       <c r="B12" t="n">
-        <v>94466</v>
+        <v>89957</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1857,39 +1858,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>210</v>
+        <v>2008</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585340</v>
+        <v>585347</v>
       </c>
       <c r="R12" t="n">
-        <v>6558598</v>
+        <v>6558564</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Vid roten på gammal kraftigt rötskadad granlåga.</t>
+          <t>8 fjolårsexemplar i barrmatta under gammal gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118526068</v>
+        <v>118525987</v>
       </c>
       <c r="B2" t="n">
-        <v>8416</v>
+        <v>91131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,36 +691,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -728,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585130</v>
+        <v>585152</v>
       </c>
       <c r="R2" t="n">
-        <v>6558822</v>
+        <v>6558846</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -773,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118525987</v>
+        <v>118526068</v>
       </c>
       <c r="B3" t="n">
-        <v>91124</v>
+        <v>8416</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,30 +810,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585152</v>
+        <v>585130</v>
       </c>
       <c r="R3" t="n">
-        <v>6558846</v>
+        <v>6558822</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118659699</v>
+        <v>118658795</v>
       </c>
       <c r="B4" t="n">
-        <v>89954</v>
+        <v>94473</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,34 +935,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4189</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -970,10 +971,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585361</v>
+        <v>585109</v>
       </c>
       <c r="R4" t="n">
-        <v>6558542</v>
+        <v>6558533</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1006,6 +1007,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Vid roten på gammal granlåga. Rikligt med torrgranar som angripits av granbarkborrar. Gott om granlågor av både gamla rötskadade och färska torrgranar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118659687</v>
+        <v>118659661</v>
       </c>
       <c r="B5" t="n">
-        <v>89954</v>
+        <v>89964</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,20 +1051,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4189</v>
+        <v>2008</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1068,7 +1074,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1084,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585362</v>
+        <v>585347</v>
       </c>
       <c r="R5" t="n">
-        <v>6558555</v>
+        <v>6558564</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1124,7 +1130,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Fjolårsexemplar i barrmatta under gammal gran.</t>
+          <t>8 fjolårsexemplar i barrmatta under gammal gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,7 +1161,7 @@
         <v>118658920</v>
       </c>
       <c r="B6" t="n">
-        <v>104940</v>
+        <v>104947</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1257,7 +1263,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Björn Rösch, Rolf Olsson, Bo Karlsson, Bo Törnquist</t>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Olsson, Björn Rösch</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1267,7 +1273,7 @@
         <v>118659200</v>
       </c>
       <c r="B7" t="n">
-        <v>90504</v>
+        <v>90511</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1375,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118658795</v>
+        <v>118659613</v>
       </c>
       <c r="B8" t="n">
-        <v>94466</v>
+        <v>94473</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1410,7 +1416,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1427,10 +1433,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585109</v>
+        <v>585340</v>
       </c>
       <c r="R8" t="n">
-        <v>6558533</v>
+        <v>6558598</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1467,7 +1473,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Vid roten på gammal granlåga. Rikligt med torrgranar som angripits av granbarkborrar. Gott om granlågor av både gamla rötskadade och färska torrgranar.</t>
+          <t>Vid roten på gammal kraftigt rötskadad granlåga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,7 +1504,7 @@
         <v>118659096</v>
       </c>
       <c r="B9" t="n">
-        <v>94466</v>
+        <v>94473</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1618,7 +1624,7 @@
         <v>118659444</v>
       </c>
       <c r="B10" t="n">
-        <v>91124</v>
+        <v>91131</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1726,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118659613</v>
+        <v>118659699</v>
       </c>
       <c r="B11" t="n">
-        <v>94466</v>
+        <v>89961</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1742,21 +1748,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>4189</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1766,11 +1772,10 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1778,10 +1783,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585340</v>
+        <v>585361</v>
       </c>
       <c r="R11" t="n">
-        <v>6558598</v>
+        <v>6558542</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1814,11 +1819,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Vid roten på gammal kraftigt rötskadad granlåga.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,10 +1846,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118659661</v>
+        <v>118659687</v>
       </c>
       <c r="B12" t="n">
-        <v>89957</v>
+        <v>89961</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1858,20 +1858,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2008</v>
+        <v>4189</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585347</v>
+        <v>585362</v>
       </c>
       <c r="R12" t="n">
-        <v>6558564</v>
+        <v>6558555</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>8 fjolårsexemplar i barrmatta under gammal gran.</t>
+          <t>Fjolårsexemplar i barrmatta under gammal gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1968,7 +1968,7 @@
         <v>118714058</v>
       </c>
       <c r="B13" t="n">
-        <v>108714</v>
+        <v>108721</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118525987</v>
+        <v>118526068</v>
       </c>
       <c r="B2" t="n">
-        <v>91131</v>
+        <v>8416</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +728,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585152</v>
+        <v>585130</v>
       </c>
       <c r="R2" t="n">
-        <v>6558846</v>
+        <v>6558822</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +763,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +773,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118526068</v>
+        <v>118525987</v>
       </c>
       <c r="B3" t="n">
-        <v>8416</v>
+        <v>91131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,36 +816,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585130</v>
+        <v>585152</v>
       </c>
       <c r="R3" t="n">
-        <v>6558822</v>
+        <v>6558846</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118658795</v>
+        <v>118659444</v>
       </c>
       <c r="B4" t="n">
-        <v>94473</v>
+        <v>91131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,35 +935,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -971,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585109</v>
+        <v>585230</v>
       </c>
       <c r="R4" t="n">
-        <v>6558533</v>
+        <v>6558800</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,7 +1002,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Vid roten på gammal granlåga. Rikligt med torrgranar som angripits av granbarkborrar. Gott om granlågor av både gamla rötskadade och färska torrgranar.</t>
+          <t>På högstubbe av gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118659661</v>
+        <v>118659096</v>
       </c>
       <c r="B5" t="n">
-        <v>89964</v>
+        <v>94473</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,38 +1042,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2008</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1090,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585347</v>
+        <v>585101</v>
       </c>
       <c r="R5" t="n">
-        <v>6558564</v>
+        <v>6558610</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1130,7 +1122,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>8 fjolårsexemplar i barrmatta under gammal gran.</t>
+          <t>På kraftigt rötangripen granstubbe.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1270,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118659200</v>
+        <v>118659613</v>
       </c>
       <c r="B7" t="n">
-        <v>90511</v>
+        <v>94473</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,30 +1274,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1313,10 +1314,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585124</v>
+        <v>585340</v>
       </c>
       <c r="R7" t="n">
-        <v>6558615</v>
+        <v>6558598</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1353,7 +1354,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På granlåga. Gott om död ved i form av torrträd och lågor av gran.</t>
+          <t>Vid roten på gammal kraftigt rötskadad granlåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118659613</v>
+        <v>118659661</v>
       </c>
       <c r="B8" t="n">
-        <v>94473</v>
+        <v>89964</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,39 +1394,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>2008</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585340</v>
+        <v>585347</v>
       </c>
       <c r="R8" t="n">
-        <v>6558598</v>
+        <v>6558564</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Vid roten på gammal kraftigt rötskadad granlåga.</t>
+          <t>8 fjolårsexemplar i barrmatta under gammal gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118659096</v>
+        <v>118659699</v>
       </c>
       <c r="B9" t="n">
-        <v>94473</v>
+        <v>89961</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,35 +1517,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>4189</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1553,10 +1552,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585101</v>
+        <v>585361</v>
       </c>
       <c r="R9" t="n">
-        <v>6558610</v>
+        <v>6558542</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1589,11 +1588,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På kraftigt rötangripen granstubbe.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,10 +1615,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118659444</v>
+        <v>118659687</v>
       </c>
       <c r="B10" t="n">
-        <v>91131</v>
+        <v>89961</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1637,25 +1631,33 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1339</v>
+        <v>4189</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1664,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585230</v>
+        <v>585362</v>
       </c>
       <c r="R10" t="n">
-        <v>6558800</v>
+        <v>6558555</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1704,7 +1706,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På högstubbe av gran.</t>
+          <t>Fjolårsexemplar i barrmatta under gammal gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1732,10 +1734,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118659699</v>
+        <v>118658795</v>
       </c>
       <c r="B11" t="n">
-        <v>89961</v>
+        <v>94473</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,34 +1750,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4189</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1783,10 +1786,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585361</v>
+        <v>585109</v>
       </c>
       <c r="R11" t="n">
-        <v>6558542</v>
+        <v>6558533</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1819,6 +1822,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Vid roten på gammal granlåga. Rikligt med torrgranar som angripits av granbarkborrar. Gott om granlågor av både gamla rötskadade och färska torrgranar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,10 +1854,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118659687</v>
+        <v>118659200</v>
       </c>
       <c r="B12" t="n">
-        <v>89961</v>
+        <v>90511</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1858,37 +1866,29 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4189</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585362</v>
+        <v>585124</v>
       </c>
       <c r="R12" t="n">
-        <v>6558555</v>
+        <v>6558615</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fjolårsexemplar i barrmatta under gammal gran.</t>
+          <t>På granlåga. Gott om död ved i form av torrträd och lågor av gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2105,6 +2105,134 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120265464</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91863</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lovisetorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>585302</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6558523</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Växer under ett bestånd med tall på hällmark.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -2110,7 +2110,7 @@
         <v>120265464</v>
       </c>
       <c r="B14" t="n">
-        <v>91863</v>
+        <v>91881</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -2704,10 +2704,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121236895</v>
+        <v>121236903</v>
       </c>
       <c r="B19" t="n">
-        <v>57364</v>
+        <v>91127</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2716,25 +2716,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2742,9 +2742,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585246</v>
+        <v>585174</v>
       </c>
       <c r="R19" t="n">
-        <v>6558647</v>
+        <v>6558553</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Hackspår i basen av murket barrträd</t>
+          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2824,10 +2824,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121236903</v>
+        <v>121236895</v>
       </c>
       <c r="B20" t="n">
-        <v>91127</v>
+        <v>57364</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2836,25 +2836,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2862,9 +2862,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585174</v>
+        <v>585246</v>
       </c>
       <c r="R20" t="n">
-        <v>6558553</v>
+        <v>6558647</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
+          <t>Hackspår i basen av murket barrträd</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3748,10 +3748,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121236906</v>
+        <v>121236905</v>
       </c>
       <c r="B28" t="n">
-        <v>90687</v>
+        <v>5169</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3760,35 +3760,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3797,13 +3793,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585120</v>
+        <v>585113</v>
       </c>
       <c r="R28" t="n">
-        <v>6558607</v>
+        <v>6558608</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3863,10 +3859,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121236905</v>
+        <v>121236906</v>
       </c>
       <c r="B29" t="n">
-        <v>5169</v>
+        <v>90687</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3875,31 +3871,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3908,13 +3908,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585113</v>
+        <v>585120</v>
       </c>
       <c r="R29" t="n">
-        <v>6558608</v>
+        <v>6558607</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -2235,10 +2235,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121236894</v>
+        <v>121236902</v>
       </c>
       <c r="B15" t="n">
-        <v>94844</v>
+        <v>92008</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2247,53 +2247,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585209</v>
+        <v>585294</v>
       </c>
       <c r="R15" t="n">
-        <v>6558636</v>
+        <v>6558517</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2331,7 +2328,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2354,10 +2350,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121236893</v>
+        <v>121236891</v>
       </c>
       <c r="B16" t="n">
-        <v>91963</v>
+        <v>55953</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2366,47 +2362,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>206004</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585245</v>
+        <v>585154</v>
       </c>
       <c r="R16" t="n">
-        <v>6558734</v>
+        <v>6558832</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2469,10 +2464,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121236908</v>
+        <v>121236896</v>
       </c>
       <c r="B17" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2504,7 +2499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2518,10 +2513,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585051</v>
+        <v>585454</v>
       </c>
       <c r="R17" t="n">
-        <v>6558550</v>
+        <v>6558597</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2584,10 +2579,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121236892</v>
+        <v>121236903</v>
       </c>
       <c r="B18" t="n">
-        <v>94690</v>
+        <v>91137</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2596,50 +2591,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>210</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585209</v>
+        <v>585174</v>
       </c>
       <c r="R18" t="n">
-        <v>6558799</v>
+        <v>6558553</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2673,7 +2668,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>3 nya/färska kapslar. I basen/På rotbenet av gammal, rötad granlåga</t>
+          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2704,10 +2699,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121236903</v>
+        <v>121236893</v>
       </c>
       <c r="B19" t="n">
-        <v>91127</v>
+        <v>91973</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2716,47 +2711,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585174</v>
+        <v>585245</v>
       </c>
       <c r="R19" t="n">
-        <v>6558553</v>
+        <v>6558734</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2789,11 +2784,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2824,10 +2814,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121236895</v>
+        <v>121236899</v>
       </c>
       <c r="B20" t="n">
-        <v>57364</v>
+        <v>90132</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2836,35 +2826,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>4189</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2873,10 +2863,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585246</v>
+        <v>585358</v>
       </c>
       <c r="R20" t="n">
-        <v>6558647</v>
+        <v>6558558</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2909,11 +2899,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Hackspår i basen av murket barrträd</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2944,10 +2929,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121236901</v>
+        <v>121236895</v>
       </c>
       <c r="B21" t="n">
-        <v>94690</v>
+        <v>57367</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2956,25 +2941,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2982,9 +2967,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2993,13 +2978,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585340</v>
+        <v>585246</v>
       </c>
       <c r="R21" t="n">
-        <v>6558597</v>
+        <v>6558647</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3033,7 +3018,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1 äldre kapsel.</t>
+          <t>Hackspår i basen av murket barrträd</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3064,10 +3049,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121236907</v>
+        <v>121236898</v>
       </c>
       <c r="B22" t="n">
-        <v>91991</v>
+        <v>57504</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3080,31 +3065,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3113,10 +3093,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585060</v>
+        <v>585384</v>
       </c>
       <c r="R22" t="n">
-        <v>6558591</v>
+        <v>6558510</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3179,10 +3159,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121236898</v>
+        <v>121236905</v>
       </c>
       <c r="B23" t="n">
-        <v>57501</v>
+        <v>5169</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3191,30 +3171,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3223,10 +3204,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585384</v>
+        <v>585113</v>
       </c>
       <c r="R23" t="n">
-        <v>6558510</v>
+        <v>6558608</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3289,10 +3270,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121236899</v>
+        <v>121236908</v>
       </c>
       <c r="B24" t="n">
-        <v>90122</v>
+        <v>92008</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3301,30 +3282,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4189</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3338,13 +3319,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585358</v>
+        <v>585051</v>
       </c>
       <c r="R24" t="n">
-        <v>6558558</v>
+        <v>6558550</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3404,10 +3385,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121236891</v>
+        <v>121236892</v>
       </c>
       <c r="B25" t="n">
-        <v>55950</v>
+        <v>94700</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3416,49 +3397,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>206004</v>
+        <v>210</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585154</v>
+        <v>585209</v>
       </c>
       <c r="R25" t="n">
-        <v>6558832</v>
+        <v>6558799</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3488,6 +3470,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>3 nya/färska kapslar. I basen/På rotbenet av gammal, rötad granlåga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3518,10 +3505,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121236902</v>
+        <v>121236894</v>
       </c>
       <c r="B26" t="n">
-        <v>91998</v>
+        <v>94854</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3530,50 +3517,53 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585294</v>
+        <v>585209</v>
       </c>
       <c r="R26" t="n">
-        <v>6558517</v>
+        <v>6558636</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3611,6 +3601,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3633,10 +3624,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121236896</v>
+        <v>121236901</v>
       </c>
       <c r="B27" t="n">
-        <v>91998</v>
+        <v>94700</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3645,35 +3636,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>210</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3682,7 +3673,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585454</v>
+        <v>585340</v>
       </c>
       <c r="R27" t="n">
         <v>6558597</v>
@@ -3718,6 +3709,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1 äldre kapsel.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3748,10 +3744,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121236905</v>
+        <v>121236904</v>
       </c>
       <c r="B28" t="n">
-        <v>5169</v>
+        <v>94700</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3764,27 +3760,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100526</v>
+        <v>210</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3793,13 +3793,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585113</v>
+        <v>585098</v>
       </c>
       <c r="R28" t="n">
-        <v>6558608</v>
+        <v>6558618</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3829,6 +3829,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3862,7 +3867,7 @@
         <v>121236906</v>
       </c>
       <c r="B29" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3974,10 +3979,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121236904</v>
+        <v>121236907</v>
       </c>
       <c r="B30" t="n">
-        <v>94690</v>
+        <v>92001</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3986,35 +3991,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>210</v>
+        <v>5449</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4023,13 +4028,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585098</v>
+        <v>585060</v>
       </c>
       <c r="R30" t="n">
-        <v>6558618</v>
+        <v>6558591</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4059,11 +4064,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -3049,10 +3049,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121236898</v>
+        <v>121236905</v>
       </c>
       <c r="B22" t="n">
-        <v>57504</v>
+        <v>5169</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3061,30 +3061,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3093,10 +3094,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585384</v>
+        <v>585113</v>
       </c>
       <c r="R22" t="n">
-        <v>6558510</v>
+        <v>6558608</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3159,10 +3160,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121236905</v>
+        <v>121236898</v>
       </c>
       <c r="B23" t="n">
-        <v>5169</v>
+        <v>57504</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3171,31 +3172,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585113</v>
+        <v>585384</v>
       </c>
       <c r="R23" t="n">
-        <v>6558608</v>
+        <v>6558510</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -3049,10 +3049,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121236905</v>
+        <v>121236898</v>
       </c>
       <c r="B22" t="n">
-        <v>5169</v>
+        <v>57504</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3061,31 +3061,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3094,10 +3093,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585113</v>
+        <v>585384</v>
       </c>
       <c r="R22" t="n">
-        <v>6558608</v>
+        <v>6558510</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3160,10 +3159,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121236898</v>
+        <v>121236905</v>
       </c>
       <c r="B23" t="n">
-        <v>57504</v>
+        <v>5169</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3172,30 +3171,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585384</v>
+        <v>585113</v>
       </c>
       <c r="R23" t="n">
-        <v>6558510</v>
+        <v>6558608</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -2235,10 +2235,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121236902</v>
+        <v>121236891</v>
       </c>
       <c r="B15" t="n">
-        <v>92008</v>
+        <v>55953</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2251,46 +2251,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>206004</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585294</v>
+        <v>585154</v>
       </c>
       <c r="R15" t="n">
-        <v>6558517</v>
+        <v>6558832</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2350,10 +2349,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121236891</v>
+        <v>121236901</v>
       </c>
       <c r="B16" t="n">
-        <v>55953</v>
+        <v>94700</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2362,25 +2361,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>206004</v>
+        <v>210</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2388,23 +2387,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585154</v>
+        <v>585340</v>
       </c>
       <c r="R16" t="n">
-        <v>6558832</v>
+        <v>6558597</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2434,6 +2434,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1 äldre kapsel.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2464,10 +2469,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121236896</v>
+        <v>121236903</v>
       </c>
       <c r="B17" t="n">
-        <v>92008</v>
+        <v>91137</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2476,35 +2481,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2513,13 +2518,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585454</v>
+        <v>585174</v>
       </c>
       <c r="R17" t="n">
-        <v>6558597</v>
+        <v>6558553</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2549,6 +2554,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2579,10 +2589,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121236903</v>
+        <v>121236894</v>
       </c>
       <c r="B18" t="n">
-        <v>91137</v>
+        <v>94854</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2591,47 +2601,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585174</v>
+        <v>585209</v>
       </c>
       <c r="R18" t="n">
-        <v>6558553</v>
+        <v>6558636</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2666,17 +2679,13 @@
           <t>2024-10-15</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2699,10 +2708,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121236893</v>
+        <v>121236892</v>
       </c>
       <c r="B19" t="n">
-        <v>91973</v>
+        <v>94700</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2715,31 +2724,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>210</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2748,13 +2757,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585245</v>
+        <v>585209</v>
       </c>
       <c r="R19" t="n">
-        <v>6558734</v>
+        <v>6558799</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2784,6 +2793,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>3 nya/färska kapslar. I basen/På rotbenet av gammal, rötad granlåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2814,10 +2828,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121236899</v>
+        <v>121236907</v>
       </c>
       <c r="B20" t="n">
-        <v>90132</v>
+        <v>92001</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2826,30 +2840,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4189</v>
+        <v>5449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2863,10 +2877,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585358</v>
+        <v>585060</v>
       </c>
       <c r="R20" t="n">
-        <v>6558558</v>
+        <v>6558591</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2929,10 +2943,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121236895</v>
+        <v>121236906</v>
       </c>
       <c r="B21" t="n">
-        <v>57367</v>
+        <v>90697</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2945,21 +2959,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2967,9 +2981,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2978,13 +2992,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585246</v>
+        <v>585120</v>
       </c>
       <c r="R21" t="n">
-        <v>6558647</v>
+        <v>6558607</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3014,11 +3028,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Hackspår i basen av murket barrträd</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3049,10 +3058,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121236898</v>
+        <v>121236899</v>
       </c>
       <c r="B22" t="n">
-        <v>57504</v>
+        <v>90132</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3061,30 +3070,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>4189</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3093,10 +3107,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585384</v>
+        <v>585358</v>
       </c>
       <c r="R22" t="n">
-        <v>6558510</v>
+        <v>6558558</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3270,10 +3284,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121236908</v>
+        <v>121236898</v>
       </c>
       <c r="B24" t="n">
-        <v>92008</v>
+        <v>57504</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3286,31 +3300,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3319,13 +3328,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585051</v>
+        <v>585384</v>
       </c>
       <c r="R24" t="n">
-        <v>6558550</v>
+        <v>6558510</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3385,10 +3394,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121236892</v>
+        <v>121236896</v>
       </c>
       <c r="B25" t="n">
-        <v>94700</v>
+        <v>92008</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3397,47 +3406,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>210</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585209</v>
+        <v>585454</v>
       </c>
       <c r="R25" t="n">
-        <v>6558799</v>
+        <v>6558597</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3470,11 +3479,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>3 nya/färska kapslar. I basen/På rotbenet av gammal, rötad granlåga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3505,10 +3509,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121236894</v>
+        <v>121236893</v>
       </c>
       <c r="B26" t="n">
-        <v>94854</v>
+        <v>91973</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3521,46 +3525,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585209</v>
+        <v>585245</v>
       </c>
       <c r="R26" t="n">
-        <v>6558636</v>
+        <v>6558734</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3601,7 +3602,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3624,10 +3624,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121236901</v>
+        <v>121236895</v>
       </c>
       <c r="B27" t="n">
-        <v>94700</v>
+        <v>57367</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3636,25 +3636,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3662,9 +3662,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3673,13 +3673,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585340</v>
+        <v>585246</v>
       </c>
       <c r="R27" t="n">
-        <v>6558597</v>
+        <v>6558647</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>1 äldre kapsel.</t>
+          <t>Hackspår i basen av murket barrträd</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3864,10 +3864,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121236906</v>
+        <v>121236908</v>
       </c>
       <c r="B29" t="n">
-        <v>90697</v>
+        <v>92008</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3880,26 +3880,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3913,10 +3913,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585120</v>
+        <v>585051</v>
       </c>
       <c r="R29" t="n">
-        <v>6558607</v>
+        <v>6558550</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121236907</v>
+        <v>121236902</v>
       </c>
       <c r="B30" t="n">
-        <v>92001</v>
+        <v>92008</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3995,26 +3995,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4028,13 +4028,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585060</v>
+        <v>585294</v>
       </c>
       <c r="R30" t="n">
-        <v>6558591</v>
+        <v>6558517</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -2235,10 +2235,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121236891</v>
+        <v>121236899</v>
       </c>
       <c r="B15" t="n">
-        <v>55953</v>
+        <v>90140</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2247,46 +2247,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>206004</v>
+        <v>4189</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585154</v>
+        <v>585358</v>
       </c>
       <c r="R15" t="n">
-        <v>6558832</v>
+        <v>6558558</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2349,10 +2350,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121236901</v>
+        <v>121236905</v>
       </c>
       <c r="B16" t="n">
-        <v>94700</v>
+        <v>5169</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2365,31 +2366,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2398,13 +2395,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585340</v>
+        <v>585113</v>
       </c>
       <c r="R16" t="n">
-        <v>6558597</v>
+        <v>6558608</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2434,11 +2431,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>1 äldre kapsel.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2469,10 +2461,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121236903</v>
+        <v>121236901</v>
       </c>
       <c r="B17" t="n">
-        <v>91137</v>
+        <v>94712</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2481,25 +2473,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>210</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2509,7 +2501,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2518,13 +2510,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585174</v>
+        <v>585340</v>
       </c>
       <c r="R17" t="n">
-        <v>6558553</v>
+        <v>6558597</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2558,7 +2550,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
+          <t>1 äldre kapsel.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2589,10 +2581,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121236894</v>
+        <v>121236908</v>
       </c>
       <c r="B18" t="n">
-        <v>94854</v>
+        <v>92020</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2601,53 +2593,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585209</v>
+        <v>585051</v>
       </c>
       <c r="R18" t="n">
-        <v>6558636</v>
+        <v>6558550</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2685,7 +2674,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2708,10 +2696,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121236892</v>
+        <v>121236896</v>
       </c>
       <c r="B19" t="n">
-        <v>94700</v>
+        <v>92020</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2720,47 +2708,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>210</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585209</v>
+        <v>585454</v>
       </c>
       <c r="R19" t="n">
-        <v>6558799</v>
+        <v>6558597</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2793,11 +2781,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>3 nya/färska kapslar. I basen/På rotbenet av gammal, rötad granlåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2828,10 +2811,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121236907</v>
+        <v>121236893</v>
       </c>
       <c r="B20" t="n">
-        <v>92001</v>
+        <v>91985</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2840,30 +2823,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2873,14 +2856,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585060</v>
+        <v>585245</v>
       </c>
       <c r="R20" t="n">
-        <v>6558591</v>
+        <v>6558734</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2943,10 +2926,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121236906</v>
+        <v>121236898</v>
       </c>
       <c r="B21" t="n">
-        <v>90697</v>
+        <v>57504</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2959,21 +2942,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2981,24 +2964,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585120</v>
+        <v>585384</v>
       </c>
       <c r="R21" t="n">
-        <v>6558607</v>
+        <v>6558510</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3058,10 +3036,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121236899</v>
+        <v>121236904</v>
       </c>
       <c r="B22" t="n">
-        <v>90132</v>
+        <v>94712</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3074,31 +3052,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4189</v>
+        <v>210</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3107,13 +3085,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585358</v>
+        <v>585098</v>
       </c>
       <c r="R22" t="n">
-        <v>6558558</v>
+        <v>6558618</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3143,6 +3121,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3173,10 +3156,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121236905</v>
+        <v>121236903</v>
       </c>
       <c r="B23" t="n">
-        <v>5169</v>
+        <v>91149</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3185,31 +3168,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3218,10 +3205,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585113</v>
+        <v>585174</v>
       </c>
       <c r="R23" t="n">
-        <v>6558608</v>
+        <v>6558553</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3254,6 +3241,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3284,10 +3276,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121236898</v>
+        <v>121236907</v>
       </c>
       <c r="B24" t="n">
-        <v>57504</v>
+        <v>92013</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3300,26 +3292,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3328,10 +3325,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585384</v>
+        <v>585060</v>
       </c>
       <c r="R24" t="n">
-        <v>6558510</v>
+        <v>6558591</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3394,10 +3391,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121236896</v>
+        <v>121236891</v>
       </c>
       <c r="B25" t="n">
-        <v>92008</v>
+        <v>55953</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3410,46 +3407,45 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>206004</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585454</v>
+        <v>585154</v>
       </c>
       <c r="R25" t="n">
-        <v>6558597</v>
+        <v>6558832</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3509,10 +3505,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121236893</v>
+        <v>121236894</v>
       </c>
       <c r="B26" t="n">
-        <v>91973</v>
+        <v>94866</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3525,43 +3521,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585245</v>
+        <v>585209</v>
       </c>
       <c r="R26" t="n">
-        <v>6558734</v>
+        <v>6558636</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3602,6 +3601,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3744,10 +3744,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121236904</v>
+        <v>121236902</v>
       </c>
       <c r="B28" t="n">
-        <v>94700</v>
+        <v>92020</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3756,35 +3756,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>210</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585098</v>
+        <v>585294</v>
       </c>
       <c r="R28" t="n">
-        <v>6558618</v>
+        <v>6558517</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3829,11 +3829,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3864,10 +3859,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121236908</v>
+        <v>121236906</v>
       </c>
       <c r="B29" t="n">
-        <v>92008</v>
+        <v>90709</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3880,26 +3875,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3913,10 +3908,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585051</v>
+        <v>585120</v>
       </c>
       <c r="R29" t="n">
-        <v>6558550</v>
+        <v>6558607</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3979,10 +3974,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121236902</v>
+        <v>121236892</v>
       </c>
       <c r="B30" t="n">
-        <v>92008</v>
+        <v>94712</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3991,47 +3986,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5966</v>
+        <v>210</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585294</v>
+        <v>585209</v>
       </c>
       <c r="R30" t="n">
-        <v>6558517</v>
+        <v>6558799</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4064,6 +4059,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>3 nya/färska kapslar. I basen/På rotbenet av gammal, rötad granlåga</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -2235,10 +2235,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121236899</v>
+        <v>121236904</v>
       </c>
       <c r="B15" t="n">
-        <v>90140</v>
+        <v>94713</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2251,31 +2251,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4189</v>
+        <v>210</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585358</v>
+        <v>585098</v>
       </c>
       <c r="R15" t="n">
-        <v>6558558</v>
+        <v>6558618</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2320,6 +2320,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2350,10 +2355,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121236905</v>
+        <v>121236894</v>
       </c>
       <c r="B16" t="n">
-        <v>5169</v>
+        <v>94867</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2366,39 +2371,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585113</v>
+        <v>585209</v>
       </c>
       <c r="R16" t="n">
-        <v>6558608</v>
+        <v>6558636</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2439,6 +2451,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2461,10 +2474,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121236901</v>
+        <v>121236896</v>
       </c>
       <c r="B17" t="n">
-        <v>94712</v>
+        <v>92021</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2473,35 +2486,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>210</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2510,7 +2523,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585340</v>
+        <v>585454</v>
       </c>
       <c r="R17" t="n">
         <v>6558597</v>
@@ -2546,11 +2559,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>1 äldre kapsel.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2581,10 +2589,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121236908</v>
+        <v>121236901</v>
       </c>
       <c r="B18" t="n">
-        <v>92020</v>
+        <v>94713</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2593,35 +2601,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>210</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2630,10 +2638,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585051</v>
+        <v>585340</v>
       </c>
       <c r="R18" t="n">
-        <v>6558550</v>
+        <v>6558597</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2666,6 +2674,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1 äldre kapsel.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2696,10 +2709,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121236896</v>
+        <v>121236908</v>
       </c>
       <c r="B19" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2731,7 +2744,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2745,10 +2758,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585454</v>
+        <v>585051</v>
       </c>
       <c r="R19" t="n">
-        <v>6558597</v>
+        <v>6558550</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2811,10 +2824,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121236893</v>
+        <v>121236895</v>
       </c>
       <c r="B20" t="n">
-        <v>91985</v>
+        <v>57367</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2823,47 +2836,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585245</v>
+        <v>585246</v>
       </c>
       <c r="R20" t="n">
-        <v>6558734</v>
+        <v>6558647</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2896,6 +2909,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hackspår i basen av murket barrträd</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2926,10 +2944,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121236898</v>
+        <v>121236906</v>
       </c>
       <c r="B21" t="n">
-        <v>57504</v>
+        <v>90710</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2942,21 +2960,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2964,19 +2982,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585384</v>
+        <v>585120</v>
       </c>
       <c r="R21" t="n">
-        <v>6558510</v>
+        <v>6558607</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3036,10 +3059,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121236904</v>
+        <v>121236899</v>
       </c>
       <c r="B22" t="n">
-        <v>94712</v>
+        <v>90141</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3052,31 +3075,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>210</v>
+        <v>4189</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3085,13 +3108,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585098</v>
+        <v>585358</v>
       </c>
       <c r="R22" t="n">
-        <v>6558618</v>
+        <v>6558558</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3121,11 +3144,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3156,10 +3174,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121236903</v>
+        <v>121236902</v>
       </c>
       <c r="B23" t="n">
-        <v>91149</v>
+        <v>92021</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3168,35 +3186,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3205,13 +3223,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585174</v>
+        <v>585294</v>
       </c>
       <c r="R23" t="n">
-        <v>6558553</v>
+        <v>6558517</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3241,11 +3259,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3276,10 +3289,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121236907</v>
+        <v>121236891</v>
       </c>
       <c r="B24" t="n">
-        <v>92013</v>
+        <v>55953</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3292,43 +3305,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>206004</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585060</v>
+        <v>585154</v>
       </c>
       <c r="R24" t="n">
-        <v>6558591</v>
+        <v>6558832</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3391,10 +3403,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121236891</v>
+        <v>121236898</v>
       </c>
       <c r="B25" t="n">
-        <v>55953</v>
+        <v>57504</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3407,21 +3419,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3429,20 +3441,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585154</v>
+        <v>585384</v>
       </c>
       <c r="R25" t="n">
-        <v>6558832</v>
+        <v>6558510</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3505,10 +3513,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121236894</v>
+        <v>121236907</v>
       </c>
       <c r="B26" t="n">
-        <v>94866</v>
+        <v>92014</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3517,50 +3525,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585209</v>
+        <v>585060</v>
       </c>
       <c r="R26" t="n">
-        <v>6558636</v>
+        <v>6558591</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3601,7 +3606,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3624,10 +3628,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121236895</v>
+        <v>121236892</v>
       </c>
       <c r="B27" t="n">
-        <v>57367</v>
+        <v>94713</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3636,50 +3640,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585246</v>
+        <v>585209</v>
       </c>
       <c r="R27" t="n">
-        <v>6558647</v>
+        <v>6558799</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3713,7 +3717,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Hackspår i basen av murket barrträd</t>
+          <t>3 nya/färska kapslar. I basen/På rotbenet av gammal, rötad granlåga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3744,10 +3748,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121236902</v>
+        <v>121236893</v>
       </c>
       <c r="B28" t="n">
-        <v>92020</v>
+        <v>91986</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3756,30 +3760,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3789,17 +3793,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585294</v>
+        <v>585245</v>
       </c>
       <c r="R28" t="n">
-        <v>6558517</v>
+        <v>6558734</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3859,10 +3863,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121236906</v>
+        <v>121236905</v>
       </c>
       <c r="B29" t="n">
-        <v>90709</v>
+        <v>5169</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3871,35 +3875,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3908,13 +3908,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585120</v>
+        <v>585113</v>
       </c>
       <c r="R29" t="n">
-        <v>6558607</v>
+        <v>6558608</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3974,10 +3974,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121236892</v>
+        <v>121236903</v>
       </c>
       <c r="B30" t="n">
-        <v>94712</v>
+        <v>91150</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3986,50 +3986,50 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>210</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585209</v>
+        <v>585174</v>
       </c>
       <c r="R30" t="n">
-        <v>6558799</v>
+        <v>6558553</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>3 nya/färska kapslar. I basen/På rotbenet av gammal, rötad granlåga</t>
+          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -2235,10 +2235,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121236904</v>
+        <v>121236898</v>
       </c>
       <c r="B15" t="n">
-        <v>94713</v>
+        <v>57507</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2247,35 +2247,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>210</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2284,13 +2279,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585098</v>
+        <v>585384</v>
       </c>
       <c r="R15" t="n">
-        <v>6558618</v>
+        <v>6558510</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2320,11 +2315,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2355,10 +2345,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121236894</v>
+        <v>121236901</v>
       </c>
       <c r="B16" t="n">
-        <v>94867</v>
+        <v>94716</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2371,49 +2361,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>210</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585209</v>
+        <v>585340</v>
       </c>
       <c r="R16" t="n">
-        <v>6558636</v>
+        <v>6558597</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2445,13 +2432,17 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1 äldre kapsel.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2474,10 +2465,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121236896</v>
+        <v>121236894</v>
       </c>
       <c r="B17" t="n">
-        <v>92021</v>
+        <v>94870</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2486,50 +2477,53 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585454</v>
+        <v>585209</v>
       </c>
       <c r="R17" t="n">
-        <v>6558597</v>
+        <v>6558636</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2567,6 +2561,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2589,10 +2584,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121236901</v>
+        <v>121236896</v>
       </c>
       <c r="B18" t="n">
-        <v>94713</v>
+        <v>92024</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2601,35 +2596,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>210</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2638,7 +2633,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585340</v>
+        <v>585454</v>
       </c>
       <c r="R18" t="n">
         <v>6558597</v>
@@ -2674,11 +2669,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>1 äldre kapsel.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2712,7 +2702,7 @@
         <v>121236908</v>
       </c>
       <c r="B19" t="n">
-        <v>92021</v>
+        <v>92024</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2827,7 +2817,7 @@
         <v>121236895</v>
       </c>
       <c r="B20" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2944,10 +2934,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121236906</v>
+        <v>121236893</v>
       </c>
       <c r="B21" t="n">
-        <v>90710</v>
+        <v>91989</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2956,30 +2946,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2989,17 +2979,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585120</v>
+        <v>585245</v>
       </c>
       <c r="R21" t="n">
-        <v>6558607</v>
+        <v>6558734</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3059,10 +3049,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121236899</v>
+        <v>121236902</v>
       </c>
       <c r="B22" t="n">
-        <v>90141</v>
+        <v>92024</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3071,30 +3061,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4189</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3108,13 +3098,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585358</v>
+        <v>585294</v>
       </c>
       <c r="R22" t="n">
-        <v>6558558</v>
+        <v>6558517</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3174,10 +3164,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121236902</v>
+        <v>121236906</v>
       </c>
       <c r="B23" t="n">
-        <v>92021</v>
+        <v>90713</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3190,26 +3180,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3223,10 +3213,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585294</v>
+        <v>585120</v>
       </c>
       <c r="R23" t="n">
-        <v>6558517</v>
+        <v>6558607</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3289,10 +3279,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121236891</v>
+        <v>121236903</v>
       </c>
       <c r="B24" t="n">
-        <v>55953</v>
+        <v>91153</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3301,25 +3291,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>206004</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3327,20 +3317,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585154</v>
+        <v>585174</v>
       </c>
       <c r="R24" t="n">
-        <v>6558832</v>
+        <v>6558553</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3373,6 +3364,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3403,10 +3399,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121236898</v>
+        <v>121236904</v>
       </c>
       <c r="B25" t="n">
-        <v>57504</v>
+        <v>94716</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3415,30 +3411,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>210</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3447,13 +3448,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585384</v>
+        <v>585098</v>
       </c>
       <c r="R25" t="n">
-        <v>6558510</v>
+        <v>6558618</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3483,6 +3484,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3513,10 +3519,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121236907</v>
+        <v>121236899</v>
       </c>
       <c r="B26" t="n">
-        <v>92014</v>
+        <v>90144</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3525,30 +3531,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5449</v>
+        <v>4189</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3562,10 +3568,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585060</v>
+        <v>585358</v>
       </c>
       <c r="R26" t="n">
-        <v>6558591</v>
+        <v>6558558</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3631,7 +3637,7 @@
         <v>121236892</v>
       </c>
       <c r="B27" t="n">
-        <v>94713</v>
+        <v>94716</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3748,10 +3754,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121236893</v>
+        <v>121236905</v>
       </c>
       <c r="B28" t="n">
-        <v>91986</v>
+        <v>5172</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3764,43 +3770,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585245</v>
+        <v>585113</v>
       </c>
       <c r="R28" t="n">
-        <v>6558734</v>
+        <v>6558608</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3863,10 +3865,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121236905</v>
+        <v>121236907</v>
       </c>
       <c r="B29" t="n">
-        <v>5169</v>
+        <v>92017</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3875,31 +3877,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>5449</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3908,10 +3914,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585113</v>
+        <v>585060</v>
       </c>
       <c r="R29" t="n">
-        <v>6558608</v>
+        <v>6558591</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3974,10 +3980,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121236903</v>
+        <v>121236891</v>
       </c>
       <c r="B30" t="n">
-        <v>91150</v>
+        <v>55956</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3986,25 +3992,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>206004</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4012,21 +4018,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585174</v>
+        <v>585154</v>
       </c>
       <c r="R30" t="n">
-        <v>6558553</v>
+        <v>6558832</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4059,11 +4064,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -2235,10 +2235,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121236898</v>
+        <v>121236908</v>
       </c>
       <c r="B15" t="n">
-        <v>57507</v>
+        <v>92024</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2251,26 +2251,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2279,13 +2284,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585384</v>
+        <v>585051</v>
       </c>
       <c r="R15" t="n">
-        <v>6558510</v>
+        <v>6558550</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2465,10 +2470,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121236894</v>
+        <v>121236902</v>
       </c>
       <c r="B17" t="n">
-        <v>94870</v>
+        <v>92024</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2477,53 +2482,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585209</v>
+        <v>585294</v>
       </c>
       <c r="R17" t="n">
-        <v>6558636</v>
+        <v>6558517</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2561,7 +2563,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2584,10 +2585,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121236896</v>
+        <v>121236898</v>
       </c>
       <c r="B18" t="n">
-        <v>92024</v>
+        <v>57507</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2600,31 +2601,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2633,13 +2629,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585454</v>
+        <v>585384</v>
       </c>
       <c r="R18" t="n">
-        <v>6558597</v>
+        <v>6558510</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2699,10 +2695,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121236908</v>
+        <v>121236892</v>
       </c>
       <c r="B19" t="n">
-        <v>92024</v>
+        <v>94716</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2711,47 +2707,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>210</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585051</v>
+        <v>585209</v>
       </c>
       <c r="R19" t="n">
-        <v>6558550</v>
+        <v>6558799</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2784,6 +2780,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>3 nya/färska kapslar. I basen/På rotbenet av gammal, rötad granlåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2934,10 +2935,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121236893</v>
+        <v>121236907</v>
       </c>
       <c r="B21" t="n">
-        <v>91989</v>
+        <v>92017</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2946,30 +2947,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2979,14 +2980,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585245</v>
+        <v>585060</v>
       </c>
       <c r="R21" t="n">
-        <v>6558734</v>
+        <v>6558591</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3049,10 +3050,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121236902</v>
+        <v>121236904</v>
       </c>
       <c r="B22" t="n">
-        <v>92024</v>
+        <v>94716</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3061,35 +3062,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>210</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3098,10 +3099,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585294</v>
+        <v>585098</v>
       </c>
       <c r="R22" t="n">
-        <v>6558517</v>
+        <v>6558618</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3134,6 +3135,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3164,10 +3170,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121236906</v>
+        <v>121236899</v>
       </c>
       <c r="B23" t="n">
-        <v>90713</v>
+        <v>90144</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3176,30 +3182,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>4189</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3213,13 +3219,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585120</v>
+        <v>585358</v>
       </c>
       <c r="R23" t="n">
-        <v>6558607</v>
+        <v>6558558</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3279,10 +3285,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121236903</v>
+        <v>121236905</v>
       </c>
       <c r="B24" t="n">
-        <v>91153</v>
+        <v>5172</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3291,35 +3297,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3328,10 +3330,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585174</v>
+        <v>585113</v>
       </c>
       <c r="R24" t="n">
-        <v>6558553</v>
+        <v>6558608</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3364,11 +3366,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3399,10 +3396,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121236904</v>
+        <v>121236906</v>
       </c>
       <c r="B25" t="n">
-        <v>94716</v>
+        <v>90713</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3411,35 +3408,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3448,10 +3445,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585098</v>
+        <v>585120</v>
       </c>
       <c r="R25" t="n">
-        <v>6558618</v>
+        <v>6558607</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3484,11 +3481,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3519,10 +3511,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121236899</v>
+        <v>121236896</v>
       </c>
       <c r="B26" t="n">
-        <v>90144</v>
+        <v>92024</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3531,30 +3523,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4189</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3568,13 +3560,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585358</v>
+        <v>585454</v>
       </c>
       <c r="R26" t="n">
-        <v>6558558</v>
+        <v>6558597</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3634,10 +3626,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121236892</v>
+        <v>121236894</v>
       </c>
       <c r="B27" t="n">
-        <v>94716</v>
+        <v>94870</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3650,46 +3642,49 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>210</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
         <v>585209</v>
       </c>
       <c r="R27" t="n">
-        <v>6558799</v>
+        <v>6558636</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3721,17 +3716,13 @@
           <t>2024-10-15</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>3 nya/färska kapslar. I basen/På rotbenet av gammal, rötad granlåga</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3754,10 +3745,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121236905</v>
+        <v>121236893</v>
       </c>
       <c r="B28" t="n">
-        <v>5172</v>
+        <v>91989</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3770,39 +3761,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585113</v>
+        <v>585245</v>
       </c>
       <c r="R28" t="n">
-        <v>6558608</v>
+        <v>6558734</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3865,10 +3860,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121236907</v>
+        <v>121236903</v>
       </c>
       <c r="B29" t="n">
-        <v>92017</v>
+        <v>91153</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3877,35 +3872,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5449</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3914,10 +3909,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585060</v>
+        <v>585174</v>
       </c>
       <c r="R29" t="n">
-        <v>6558591</v>
+        <v>6558553</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3950,6 +3945,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -2695,10 +2695,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121236892</v>
+        <v>121236895</v>
       </c>
       <c r="B19" t="n">
-        <v>94716</v>
+        <v>57370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2707,50 +2707,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585209</v>
+        <v>585246</v>
       </c>
       <c r="R19" t="n">
-        <v>6558799</v>
+        <v>6558647</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>3 nya/färska kapslar. I basen/På rotbenet av gammal, rötad granlåga</t>
+          <t>Hackspår i basen av murket barrträd</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121236895</v>
+        <v>121236892</v>
       </c>
       <c r="B20" t="n">
-        <v>57370</v>
+        <v>94716</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2827,50 +2827,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585246</v>
+        <v>585209</v>
       </c>
       <c r="R20" t="n">
-        <v>6558647</v>
+        <v>6558799</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Hackspår i basen av murket barrträd</t>
+          <t>3 nya/färska kapslar. I basen/På rotbenet av gammal, rötad granlåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3050,10 +3050,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121236904</v>
+        <v>121236899</v>
       </c>
       <c r="B22" t="n">
-        <v>94716</v>
+        <v>90144</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3066,31 +3066,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>210</v>
+        <v>4189</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3099,13 +3099,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585098</v>
+        <v>585358</v>
       </c>
       <c r="R22" t="n">
-        <v>6558618</v>
+        <v>6558558</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3135,11 +3135,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3170,10 +3165,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121236899</v>
+        <v>121236904</v>
       </c>
       <c r="B23" t="n">
-        <v>90144</v>
+        <v>94716</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3186,31 +3181,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4189</v>
+        <v>210</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3219,13 +3214,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585358</v>
+        <v>585098</v>
       </c>
       <c r="R23" t="n">
-        <v>6558558</v>
+        <v>6558618</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3255,6 +3250,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -2235,10 +2235,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121236908</v>
+        <v>121236904</v>
       </c>
       <c r="B15" t="n">
-        <v>92024</v>
+        <v>94722</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2247,35 +2247,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>210</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585051</v>
+        <v>585098</v>
       </c>
       <c r="R15" t="n">
-        <v>6558550</v>
+        <v>6558618</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2320,6 +2320,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2350,10 +2355,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121236901</v>
+        <v>121236902</v>
       </c>
       <c r="B16" t="n">
-        <v>94716</v>
+        <v>92030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2362,35 +2367,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2399,10 +2404,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585340</v>
+        <v>585294</v>
       </c>
       <c r="R16" t="n">
-        <v>6558597</v>
+        <v>6558517</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2435,11 +2440,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>1 äldre kapsel.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2470,10 +2470,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121236902</v>
+        <v>121236893</v>
       </c>
       <c r="B17" t="n">
-        <v>92024</v>
+        <v>91995</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2482,30 +2482,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585294</v>
+        <v>585245</v>
       </c>
       <c r="R17" t="n">
-        <v>6558517</v>
+        <v>6558734</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2585,10 +2585,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121236898</v>
+        <v>121236896</v>
       </c>
       <c r="B18" t="n">
-        <v>57507</v>
+        <v>92030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2601,26 +2601,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2629,13 +2634,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585384</v>
+        <v>585454</v>
       </c>
       <c r="R18" t="n">
-        <v>6558510</v>
+        <v>6558597</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2695,10 +2700,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121236895</v>
+        <v>121236901</v>
       </c>
       <c r="B19" t="n">
-        <v>57370</v>
+        <v>94722</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2707,25 +2712,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2733,9 +2738,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2744,13 +2749,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585246</v>
+        <v>585340</v>
       </c>
       <c r="R19" t="n">
-        <v>6558647</v>
+        <v>6558597</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2784,7 +2789,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Hackspår i basen av murket barrträd</t>
+          <t>1 äldre kapsel.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2818,7 +2823,7 @@
         <v>121236892</v>
       </c>
       <c r="B20" t="n">
-        <v>94716</v>
+        <v>94722</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2935,10 +2940,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121236907</v>
+        <v>121236898</v>
       </c>
       <c r="B21" t="n">
-        <v>92017</v>
+        <v>57508</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2951,31 +2956,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585060</v>
+        <v>585384</v>
       </c>
       <c r="R21" t="n">
-        <v>6558591</v>
+        <v>6558510</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121236899</v>
+        <v>121236894</v>
       </c>
       <c r="B22" t="n">
-        <v>90144</v>
+        <v>94876</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3066,43 +3066,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4189</v>
+        <v>2180</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585358</v>
+        <v>585209</v>
       </c>
       <c r="R22" t="n">
-        <v>6558558</v>
+        <v>6558636</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3143,6 +3146,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3165,10 +3169,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121236904</v>
+        <v>121236899</v>
       </c>
       <c r="B23" t="n">
-        <v>94716</v>
+        <v>90150</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3181,31 +3185,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>210</v>
+        <v>4189</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3214,13 +3218,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585098</v>
+        <v>585358</v>
       </c>
       <c r="R23" t="n">
-        <v>6558618</v>
+        <v>6558558</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3250,11 +3254,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3285,10 +3284,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121236905</v>
+        <v>121236907</v>
       </c>
       <c r="B24" t="n">
-        <v>5172</v>
+        <v>92023</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3297,31 +3296,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3330,10 +3333,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585113</v>
+        <v>585060</v>
       </c>
       <c r="R24" t="n">
-        <v>6558608</v>
+        <v>6558591</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3399,7 +3402,7 @@
         <v>121236906</v>
       </c>
       <c r="B25" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3511,10 +3514,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121236896</v>
+        <v>121236905</v>
       </c>
       <c r="B26" t="n">
-        <v>92024</v>
+        <v>5172</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3523,35 +3526,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3560,13 +3559,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585454</v>
+        <v>585113</v>
       </c>
       <c r="R26" t="n">
-        <v>6558597</v>
+        <v>6558608</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3626,10 +3625,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121236894</v>
+        <v>121236908</v>
       </c>
       <c r="B27" t="n">
-        <v>94870</v>
+        <v>92030</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3638,53 +3637,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585209</v>
+        <v>585051</v>
       </c>
       <c r="R27" t="n">
-        <v>6558636</v>
+        <v>6558550</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3722,7 +3718,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3745,10 +3740,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121236893</v>
+        <v>121236895</v>
       </c>
       <c r="B28" t="n">
-        <v>91989</v>
+        <v>57371</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3757,47 +3752,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585245</v>
+        <v>585246</v>
       </c>
       <c r="R28" t="n">
-        <v>6558734</v>
+        <v>6558647</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3830,6 +3825,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hackspår i basen av murket barrträd</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3863,7 +3863,7 @@
         <v>121236903</v>
       </c>
       <c r="B29" t="n">
-        <v>91153</v>
+        <v>91159</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>121236891</v>
       </c>
       <c r="B30" t="n">
-        <v>55956</v>
+        <v>55957</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -2235,10 +2235,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121236904</v>
+        <v>121236902</v>
       </c>
       <c r="B15" t="n">
-        <v>94722</v>
+        <v>92030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2247,35 +2247,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>210</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585098</v>
+        <v>585294</v>
       </c>
       <c r="R15" t="n">
-        <v>6558618</v>
+        <v>6558517</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2320,11 +2320,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2355,10 +2350,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121236902</v>
+        <v>121236904</v>
       </c>
       <c r="B16" t="n">
-        <v>92030</v>
+        <v>94722</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2367,35 +2362,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>210</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2404,10 +2399,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585294</v>
+        <v>585098</v>
       </c>
       <c r="R16" t="n">
-        <v>6558517</v>
+        <v>6558618</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2440,6 +2435,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3860,10 +3860,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121236903</v>
+        <v>121236891</v>
       </c>
       <c r="B29" t="n">
-        <v>91159</v>
+        <v>55957</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3872,25 +3872,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>206004</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3898,21 +3898,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585174</v>
+        <v>585154</v>
       </c>
       <c r="R29" t="n">
-        <v>6558553</v>
+        <v>6558832</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3945,11 +3944,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3980,10 +3974,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121236891</v>
+        <v>121236903</v>
       </c>
       <c r="B30" t="n">
-        <v>55957</v>
+        <v>91159</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3992,25 +3986,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>206004</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4018,20 +4012,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585154</v>
+        <v>585174</v>
       </c>
       <c r="R30" t="n">
-        <v>6558832</v>
+        <v>6558553</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4064,6 +4059,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -2238,7 +2238,7 @@
         <v>121236902</v>
       </c>
       <c r="B15" t="n">
-        <v>92030</v>
+        <v>92031</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121236904</v>
+        <v>121236894</v>
       </c>
       <c r="B16" t="n">
-        <v>94722</v>
+        <v>94877</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2366,46 +2366,49 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585098</v>
+        <v>585209</v>
       </c>
       <c r="R16" t="n">
-        <v>6558618</v>
+        <v>6558636</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2437,17 +2440,13 @@
           <t>2024-10-15</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2470,10 +2469,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121236893</v>
+        <v>121236905</v>
       </c>
       <c r="B17" t="n">
-        <v>91995</v>
+        <v>5172</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2486,43 +2485,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585245</v>
+        <v>585113</v>
       </c>
       <c r="R17" t="n">
-        <v>6558734</v>
+        <v>6558608</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2585,10 +2580,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121236896</v>
+        <v>121236908</v>
       </c>
       <c r="B18" t="n">
-        <v>92030</v>
+        <v>92031</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2620,7 +2615,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2634,10 +2629,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585454</v>
+        <v>585051</v>
       </c>
       <c r="R18" t="n">
-        <v>6558597</v>
+        <v>6558550</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2700,10 +2695,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121236901</v>
+        <v>121236891</v>
       </c>
       <c r="B19" t="n">
-        <v>94722</v>
+        <v>55958</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2712,25 +2707,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>210</v>
+        <v>206004</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2738,24 +2733,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585340</v>
+        <v>585154</v>
       </c>
       <c r="R19" t="n">
-        <v>6558597</v>
+        <v>6558832</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2785,11 +2779,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>1 äldre kapsel.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2820,10 +2809,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121236892</v>
+        <v>121236903</v>
       </c>
       <c r="B20" t="n">
-        <v>94722</v>
+        <v>91160</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2832,50 +2821,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>210</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585209</v>
+        <v>585174</v>
       </c>
       <c r="R20" t="n">
-        <v>6558799</v>
+        <v>6558553</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2909,7 +2898,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>3 nya/färska kapslar. I basen/På rotbenet av gammal, rötad granlåga</t>
+          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2940,10 +2929,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121236898</v>
+        <v>121236893</v>
       </c>
       <c r="B21" t="n">
-        <v>57508</v>
+        <v>91996</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2952,42 +2941,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585384</v>
+        <v>585245</v>
       </c>
       <c r="R21" t="n">
-        <v>6558510</v>
+        <v>6558734</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3050,10 +3044,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121236894</v>
+        <v>121236901</v>
       </c>
       <c r="B22" t="n">
-        <v>94876</v>
+        <v>94723</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3066,49 +3060,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>210</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585209</v>
+        <v>585340</v>
       </c>
       <c r="R22" t="n">
-        <v>6558636</v>
+        <v>6558597</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3140,13 +3131,17 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>1 äldre kapsel.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3169,10 +3164,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121236899</v>
+        <v>121236895</v>
       </c>
       <c r="B23" t="n">
-        <v>90150</v>
+        <v>57372</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3181,35 +3176,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4189</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3218,10 +3213,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585358</v>
+        <v>585246</v>
       </c>
       <c r="R23" t="n">
-        <v>6558558</v>
+        <v>6558647</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3254,6 +3249,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hackspår i basen av murket barrträd</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3284,10 +3284,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121236907</v>
+        <v>121236896</v>
       </c>
       <c r="B24" t="n">
-        <v>92023</v>
+        <v>92031</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3300,26 +3300,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3333,13 +3333,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585060</v>
+        <v>585454</v>
       </c>
       <c r="R24" t="n">
-        <v>6558591</v>
+        <v>6558597</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3399,10 +3399,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121236906</v>
+        <v>121236904</v>
       </c>
       <c r="B25" t="n">
-        <v>90719</v>
+        <v>94723</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3411,35 +3411,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585120</v>
+        <v>585098</v>
       </c>
       <c r="R25" t="n">
-        <v>6558607</v>
+        <v>6558618</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3484,6 +3484,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3514,10 +3519,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121236905</v>
+        <v>121236899</v>
       </c>
       <c r="B26" t="n">
-        <v>5172</v>
+        <v>90151</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3530,27 +3535,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100526</v>
+        <v>4189</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3559,10 +3568,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585113</v>
+        <v>585358</v>
       </c>
       <c r="R26" t="n">
-        <v>6558608</v>
+        <v>6558558</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3625,10 +3634,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121236908</v>
+        <v>121236907</v>
       </c>
       <c r="B27" t="n">
-        <v>92030</v>
+        <v>92024</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3641,26 +3650,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3674,13 +3683,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585051</v>
+        <v>585060</v>
       </c>
       <c r="R27" t="n">
-        <v>6558550</v>
+        <v>6558591</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3740,10 +3749,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121236895</v>
+        <v>121236892</v>
       </c>
       <c r="B28" t="n">
-        <v>57371</v>
+        <v>94723</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3752,50 +3761,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585246</v>
+        <v>585209</v>
       </c>
       <c r="R28" t="n">
-        <v>6558647</v>
+        <v>6558799</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3829,7 +3838,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Hackspår i basen av murket barrträd</t>
+          <t>3 nya/färska kapslar. I basen/På rotbenet av gammal, rötad granlåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3860,10 +3869,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121236891</v>
+        <v>121236898</v>
       </c>
       <c r="B29" t="n">
-        <v>55957</v>
+        <v>57509</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3876,21 +3885,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3898,20 +3907,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585154</v>
+        <v>585384</v>
       </c>
       <c r="R29" t="n">
-        <v>6558832</v>
+        <v>6558510</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3974,10 +3979,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121236903</v>
+        <v>121236906</v>
       </c>
       <c r="B30" t="n">
-        <v>91159</v>
+        <v>90720</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3986,25 +3991,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4014,7 +4019,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4023,13 +4028,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585174</v>
+        <v>585120</v>
       </c>
       <c r="R30" t="n">
-        <v>6558553</v>
+        <v>6558607</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4059,11 +4064,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -2235,10 +2235,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121236902</v>
+        <v>121236899</v>
       </c>
       <c r="B15" t="n">
-        <v>92031</v>
+        <v>90151</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2247,30 +2247,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>4189</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585294</v>
+        <v>585358</v>
       </c>
       <c r="R15" t="n">
-        <v>6558517</v>
+        <v>6558558</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121236894</v>
+        <v>121236892</v>
       </c>
       <c r="B16" t="n">
-        <v>94877</v>
+        <v>94723</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2366,49 +2366,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>210</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
         <v>585209</v>
       </c>
       <c r="R16" t="n">
-        <v>6558636</v>
+        <v>6558799</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2440,13 +2437,17 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>3 nya/färska kapslar. I basen/På rotbenet av gammal, rötad granlåga</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2469,10 +2470,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121236905</v>
+        <v>121236906</v>
       </c>
       <c r="B17" t="n">
-        <v>5172</v>
+        <v>90720</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2481,31 +2482,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2514,13 +2519,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585113</v>
+        <v>585120</v>
       </c>
       <c r="R17" t="n">
-        <v>6558608</v>
+        <v>6558607</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2580,10 +2585,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121236908</v>
+        <v>121236907</v>
       </c>
       <c r="B18" t="n">
-        <v>92031</v>
+        <v>92024</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2596,26 +2601,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2629,13 +2634,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585051</v>
+        <v>585060</v>
       </c>
       <c r="R18" t="n">
-        <v>6558550</v>
+        <v>6558591</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2695,10 +2700,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121236891</v>
+        <v>121236898</v>
       </c>
       <c r="B19" t="n">
-        <v>55958</v>
+        <v>57509</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2711,21 +2716,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2733,20 +2738,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585154</v>
+        <v>585384</v>
       </c>
       <c r="R19" t="n">
-        <v>6558832</v>
+        <v>6558510</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2809,10 +2810,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121236903</v>
+        <v>121236908</v>
       </c>
       <c r="B20" t="n">
-        <v>91160</v>
+        <v>92031</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2821,35 +2822,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2858,13 +2859,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585174</v>
+        <v>585051</v>
       </c>
       <c r="R20" t="n">
-        <v>6558553</v>
+        <v>6558550</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2894,11 +2895,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2929,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121236893</v>
+        <v>121236891</v>
       </c>
       <c r="B21" t="n">
-        <v>91996</v>
+        <v>55958</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2941,47 +2937,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>206004</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585245</v>
+        <v>585154</v>
       </c>
       <c r="R21" t="n">
-        <v>6558734</v>
+        <v>6558832</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3044,10 +3039,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121236901</v>
+        <v>121236895</v>
       </c>
       <c r="B22" t="n">
-        <v>94723</v>
+        <v>57372</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3056,25 +3051,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3082,9 +3077,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3093,13 +3088,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585340</v>
+        <v>585246</v>
       </c>
       <c r="R22" t="n">
-        <v>6558597</v>
+        <v>6558647</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3133,7 +3128,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>1 äldre kapsel.</t>
+          <t>Hackspår i basen av murket barrträd</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3164,10 +3159,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121236895</v>
+        <v>121236904</v>
       </c>
       <c r="B23" t="n">
-        <v>57372</v>
+        <v>94723</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3176,35 +3171,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3213,13 +3208,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585246</v>
+        <v>585098</v>
       </c>
       <c r="R23" t="n">
-        <v>6558647</v>
+        <v>6558618</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3253,7 +3248,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Hackspår i basen av murket barrträd</t>
+          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3284,7 +3279,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121236896</v>
+        <v>121236902</v>
       </c>
       <c r="B24" t="n">
         <v>92031</v>
@@ -3333,10 +3328,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585454</v>
+        <v>585294</v>
       </c>
       <c r="R24" t="n">
-        <v>6558597</v>
+        <v>6558517</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3399,10 +3394,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121236904</v>
+        <v>121236896</v>
       </c>
       <c r="B25" t="n">
-        <v>94723</v>
+        <v>92031</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3411,35 +3406,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>210</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3448,10 +3443,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585098</v>
+        <v>585454</v>
       </c>
       <c r="R25" t="n">
-        <v>6558618</v>
+        <v>6558597</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3484,11 +3479,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3519,10 +3509,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121236899</v>
+        <v>121236894</v>
       </c>
       <c r="B26" t="n">
-        <v>90151</v>
+        <v>94877</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3535,43 +3525,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4189</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585358</v>
+        <v>585209</v>
       </c>
       <c r="R26" t="n">
-        <v>6558558</v>
+        <v>6558636</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3612,6 +3605,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3634,10 +3628,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121236907</v>
+        <v>121236903</v>
       </c>
       <c r="B27" t="n">
-        <v>92024</v>
+        <v>91160</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3646,35 +3640,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5449</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3683,10 +3677,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585060</v>
+        <v>585174</v>
       </c>
       <c r="R27" t="n">
-        <v>6558591</v>
+        <v>6558553</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3719,6 +3713,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3749,10 +3748,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121236892</v>
+        <v>121236893</v>
       </c>
       <c r="B28" t="n">
-        <v>94723</v>
+        <v>91996</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3765,31 +3764,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>210</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3798,13 +3797,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585209</v>
+        <v>585245</v>
       </c>
       <c r="R28" t="n">
-        <v>6558799</v>
+        <v>6558734</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3834,11 +3833,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>3 nya/färska kapslar. I basen/På rotbenet av gammal, rötad granlåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3869,10 +3863,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121236898</v>
+        <v>121236905</v>
       </c>
       <c r="B29" t="n">
-        <v>57509</v>
+        <v>5172</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3881,30 +3875,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3913,10 +3908,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585384</v>
+        <v>585113</v>
       </c>
       <c r="R29" t="n">
-        <v>6558510</v>
+        <v>6558608</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3979,10 +3974,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121236906</v>
+        <v>121236901</v>
       </c>
       <c r="B30" t="n">
-        <v>90720</v>
+        <v>94723</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3991,25 +3986,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4019,7 +4014,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4028,10 +4023,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585120</v>
+        <v>585340</v>
       </c>
       <c r="R30" t="n">
-        <v>6558607</v>
+        <v>6558597</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4064,6 +4059,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>1 äldre kapsel.</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -2235,10 +2235,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121236899</v>
+        <v>121236898</v>
       </c>
       <c r="B15" t="n">
-        <v>90151</v>
+        <v>57509</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2247,35 +2247,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4189</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2284,10 +2279,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585358</v>
+        <v>585384</v>
       </c>
       <c r="R15" t="n">
-        <v>6558558</v>
+        <v>6558510</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2350,10 +2345,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121236892</v>
+        <v>121236895</v>
       </c>
       <c r="B16" t="n">
-        <v>94723</v>
+        <v>57372</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2362,50 +2357,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585209</v>
+        <v>585246</v>
       </c>
       <c r="R16" t="n">
-        <v>6558799</v>
+        <v>6558647</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2439,7 +2434,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>3 nya/färska kapslar. I basen/På rotbenet av gammal, rötad granlåga</t>
+          <t>Hackspår i basen av murket barrträd</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2470,10 +2465,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121236906</v>
+        <v>121236899</v>
       </c>
       <c r="B17" t="n">
-        <v>90720</v>
+        <v>90151</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2482,30 +2477,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>4189</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2519,13 +2514,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585120</v>
+        <v>585358</v>
       </c>
       <c r="R17" t="n">
-        <v>6558607</v>
+        <v>6558558</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2585,10 +2580,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121236907</v>
+        <v>121236903</v>
       </c>
       <c r="B18" t="n">
-        <v>92024</v>
+        <v>91160</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2597,35 +2592,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5449</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2634,10 +2629,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585060</v>
+        <v>585174</v>
       </c>
       <c r="R18" t="n">
-        <v>6558591</v>
+        <v>6558553</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2670,6 +2665,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2700,10 +2700,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121236898</v>
+        <v>121236896</v>
       </c>
       <c r="B19" t="n">
-        <v>57509</v>
+        <v>92031</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2716,26 +2716,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2744,13 +2749,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585384</v>
+        <v>585454</v>
       </c>
       <c r="R19" t="n">
-        <v>6558510</v>
+        <v>6558597</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2810,10 +2815,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121236908</v>
+        <v>121236901</v>
       </c>
       <c r="B20" t="n">
-        <v>92031</v>
+        <v>94723</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2822,35 +2827,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>210</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2859,10 +2864,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585051</v>
+        <v>585340</v>
       </c>
       <c r="R20" t="n">
-        <v>6558550</v>
+        <v>6558597</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2895,6 +2900,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1 äldre kapsel.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2925,10 +2935,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121236891</v>
+        <v>121236905</v>
       </c>
       <c r="B21" t="n">
-        <v>55958</v>
+        <v>5172</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2937,46 +2947,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>206004</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585154</v>
+        <v>585113</v>
       </c>
       <c r="R21" t="n">
-        <v>6558832</v>
+        <v>6558608</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3039,10 +3046,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121236895</v>
+        <v>121236893</v>
       </c>
       <c r="B22" t="n">
-        <v>57372</v>
+        <v>91996</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3051,47 +3058,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585246</v>
+        <v>585245</v>
       </c>
       <c r="R22" t="n">
-        <v>6558647</v>
+        <v>6558734</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3124,11 +3131,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hackspår i basen av murket barrträd</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3159,7 +3161,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121236904</v>
+        <v>121236892</v>
       </c>
       <c r="B23" t="n">
         <v>94723</v>
@@ -3194,7 +3196,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3204,14 +3206,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585098</v>
+        <v>585209</v>
       </c>
       <c r="R23" t="n">
-        <v>6558618</v>
+        <v>6558799</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3248,7 +3250,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
+          <t>3 nya/färska kapslar. I basen/På rotbenet av gammal, rötad granlåga</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3279,7 +3281,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121236902</v>
+        <v>121236908</v>
       </c>
       <c r="B24" t="n">
         <v>92031</v>
@@ -3314,7 +3316,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3328,10 +3330,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585294</v>
+        <v>585051</v>
       </c>
       <c r="R24" t="n">
-        <v>6558517</v>
+        <v>6558550</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3394,10 +3396,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121236896</v>
+        <v>121236906</v>
       </c>
       <c r="B25" t="n">
-        <v>92031</v>
+        <v>90720</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3410,26 +3412,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3443,10 +3445,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585454</v>
+        <v>585120</v>
       </c>
       <c r="R25" t="n">
-        <v>6558597</v>
+        <v>6558607</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3509,10 +3511,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121236894</v>
+        <v>121236907</v>
       </c>
       <c r="B26" t="n">
-        <v>94877</v>
+        <v>92024</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3521,50 +3523,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585209</v>
+        <v>585060</v>
       </c>
       <c r="R26" t="n">
-        <v>6558636</v>
+        <v>6558591</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3605,7 +3604,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3628,10 +3626,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121236903</v>
+        <v>121236891</v>
       </c>
       <c r="B27" t="n">
-        <v>91160</v>
+        <v>55958</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3640,25 +3638,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>206004</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3666,21 +3664,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585174</v>
+        <v>585154</v>
       </c>
       <c r="R27" t="n">
-        <v>6558553</v>
+        <v>6558832</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3713,11 +3710,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3748,10 +3740,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121236893</v>
+        <v>121236902</v>
       </c>
       <c r="B28" t="n">
-        <v>91996</v>
+        <v>92031</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3760,30 +3752,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3793,17 +3785,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585245</v>
+        <v>585294</v>
       </c>
       <c r="R28" t="n">
-        <v>6558734</v>
+        <v>6558517</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3863,10 +3855,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121236905</v>
+        <v>121236904</v>
       </c>
       <c r="B29" t="n">
-        <v>5172</v>
+        <v>94723</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3879,27 +3871,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>210</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3908,13 +3904,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585113</v>
+        <v>585098</v>
       </c>
       <c r="R29" t="n">
-        <v>6558608</v>
+        <v>6558618</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3944,6 +3940,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3974,10 +3975,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121236901</v>
+        <v>121236894</v>
       </c>
       <c r="B30" t="n">
-        <v>94723</v>
+        <v>94877</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3990,46 +3991,49 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>210</v>
+        <v>2180</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585340</v>
+        <v>585209</v>
       </c>
       <c r="R30" t="n">
-        <v>6558597</v>
+        <v>6558636</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4061,17 +4065,13 @@
           <t>2024-10-15</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>1 äldre kapsel.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -2235,10 +2235,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121236898</v>
+        <v>121236902</v>
       </c>
       <c r="B15" t="n">
-        <v>57509</v>
+        <v>92031</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2251,26 +2251,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2279,13 +2284,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585384</v>
+        <v>585294</v>
       </c>
       <c r="R15" t="n">
-        <v>6558510</v>
+        <v>6558517</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2345,10 +2350,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121236895</v>
+        <v>121236898</v>
       </c>
       <c r="B16" t="n">
-        <v>57372</v>
+        <v>57509</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2361,21 +2366,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2383,21 +2388,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585246</v>
+        <v>585384</v>
       </c>
       <c r="R16" t="n">
-        <v>6558647</v>
+        <v>6558510</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2430,11 +2430,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hackspår i basen av murket barrträd</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2465,10 +2460,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121236899</v>
+        <v>121236903</v>
       </c>
       <c r="B17" t="n">
-        <v>90151</v>
+        <v>91160</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2477,35 +2472,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4189</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2514,10 +2509,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585358</v>
+        <v>585174</v>
       </c>
       <c r="R17" t="n">
-        <v>6558558</v>
+        <v>6558553</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2550,6 +2545,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2580,10 +2580,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121236903</v>
+        <v>121236896</v>
       </c>
       <c r="B18" t="n">
-        <v>91160</v>
+        <v>92031</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2592,35 +2592,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2629,13 +2629,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585174</v>
+        <v>585454</v>
       </c>
       <c r="R18" t="n">
-        <v>6558553</v>
+        <v>6558597</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2665,11 +2665,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2700,10 +2695,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121236896</v>
+        <v>121236901</v>
       </c>
       <c r="B19" t="n">
-        <v>92031</v>
+        <v>94723</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2712,35 +2707,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>210</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2749,7 +2744,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585454</v>
+        <v>585340</v>
       </c>
       <c r="R19" t="n">
         <v>6558597</v>
@@ -2785,6 +2780,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>1 äldre kapsel.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2815,7 +2815,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121236901</v>
+        <v>121236904</v>
       </c>
       <c r="B20" t="n">
         <v>94723</v>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585340</v>
+        <v>585098</v>
       </c>
       <c r="R20" t="n">
-        <v>6558597</v>
+        <v>6558618</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1 äldre kapsel.</t>
+          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2935,10 +2935,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121236905</v>
+        <v>121236892</v>
       </c>
       <c r="B21" t="n">
-        <v>5172</v>
+        <v>94723</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2951,42 +2951,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>210</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585113</v>
+        <v>585209</v>
       </c>
       <c r="R21" t="n">
-        <v>6558608</v>
+        <v>6558799</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3016,6 +3020,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>3 nya/färska kapslar. I basen/På rotbenet av gammal, rötad granlåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3046,10 +3055,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121236893</v>
+        <v>121236891</v>
       </c>
       <c r="B22" t="n">
-        <v>91996</v>
+        <v>55958</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3058,47 +3067,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>206004</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585245</v>
+        <v>585154</v>
       </c>
       <c r="R22" t="n">
-        <v>6558734</v>
+        <v>6558832</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3161,10 +3169,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121236892</v>
+        <v>121236906</v>
       </c>
       <c r="B23" t="n">
-        <v>94723</v>
+        <v>90720</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3173,47 +3181,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585209</v>
+        <v>585120</v>
       </c>
       <c r="R23" t="n">
-        <v>6558799</v>
+        <v>6558607</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3246,11 +3254,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>3 nya/färska kapslar. I basen/På rotbenet av gammal, rötad granlåga</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3281,10 +3284,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121236908</v>
+        <v>121236893</v>
       </c>
       <c r="B24" t="n">
-        <v>92031</v>
+        <v>91996</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3293,30 +3296,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3326,17 +3329,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585051</v>
+        <v>585245</v>
       </c>
       <c r="R24" t="n">
-        <v>6558550</v>
+        <v>6558734</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3396,10 +3399,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121236906</v>
+        <v>121236895</v>
       </c>
       <c r="B25" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3412,21 +3415,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3434,9 +3437,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3445,13 +3448,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585120</v>
+        <v>585246</v>
       </c>
       <c r="R25" t="n">
-        <v>6558607</v>
+        <v>6558647</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3481,6 +3484,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hackspår i basen av murket barrträd</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3511,10 +3519,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121236907</v>
+        <v>121236894</v>
       </c>
       <c r="B26" t="n">
-        <v>92024</v>
+        <v>94877</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3523,47 +3531,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585060</v>
+        <v>585209</v>
       </c>
       <c r="R26" t="n">
-        <v>6558591</v>
+        <v>6558636</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3604,6 +3615,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3626,10 +3638,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121236891</v>
+        <v>121236907</v>
       </c>
       <c r="B27" t="n">
-        <v>55958</v>
+        <v>92024</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3642,42 +3654,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>206004</v>
+        <v>5449</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585154</v>
+        <v>585060</v>
       </c>
       <c r="R27" t="n">
-        <v>6558832</v>
+        <v>6558591</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3740,7 +3753,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121236902</v>
+        <v>121236908</v>
       </c>
       <c r="B28" t="n">
         <v>92031</v>
@@ -3775,7 +3788,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3789,10 +3802,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585294</v>
+        <v>585051</v>
       </c>
       <c r="R28" t="n">
-        <v>6558517</v>
+        <v>6558550</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3855,10 +3868,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121236904</v>
+        <v>121236899</v>
       </c>
       <c r="B29" t="n">
-        <v>94723</v>
+        <v>90151</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3871,31 +3884,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>210</v>
+        <v>4189</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3904,13 +3917,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585098</v>
+        <v>585358</v>
       </c>
       <c r="R29" t="n">
-        <v>6558618</v>
+        <v>6558558</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3940,11 +3953,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3975,10 +3983,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121236894</v>
+        <v>121236905</v>
       </c>
       <c r="B30" t="n">
-        <v>94877</v>
+        <v>5172</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3991,46 +3999,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2180</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585209</v>
+        <v>585113</v>
       </c>
       <c r="R30" t="n">
-        <v>6558636</v>
+        <v>6558608</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4071,7 +4072,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4092,6 +4092,122 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128944579</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91873</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hälleforsnäs IP, Srm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>585270</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6558560</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -4097,7 +4097,7 @@
         <v>128944579</v>
       </c>
       <c r="B31" t="n">
-        <v>91873</v>
+        <v>91877</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -4097,7 +4097,7 @@
         <v>128944579</v>
       </c>
       <c r="B31" t="n">
-        <v>91877</v>
+        <v>91882</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -4097,7 +4097,7 @@
         <v>128944579</v>
       </c>
       <c r="B31" t="n">
-        <v>91890</v>
+        <v>91893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -4097,7 +4097,7 @@
         <v>128944579</v>
       </c>
       <c r="B31" t="n">
-        <v>91893</v>
+        <v>91896</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -4097,7 +4097,7 @@
         <v>128944579</v>
       </c>
       <c r="B31" t="n">
-        <v>91896</v>
+        <v>91903</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -4097,7 +4097,7 @@
         <v>128944579</v>
       </c>
       <c r="B31" t="n">
-        <v>91903</v>
+        <v>91910</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -4097,7 +4097,7 @@
         <v>128944579</v>
       </c>
       <c r="B31" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -4097,7 +4097,7 @@
         <v>128944579</v>
       </c>
       <c r="B31" t="n">
-        <v>91912</v>
+        <v>91921</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -4097,7 +4097,7 @@
         <v>128944579</v>
       </c>
       <c r="B31" t="n">
-        <v>91921</v>
+        <v>91922</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -4097,7 +4097,7 @@
         <v>128944579</v>
       </c>
       <c r="B31" t="n">
-        <v>91922</v>
+        <v>91925</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -4097,7 +4097,7 @@
         <v>128944579</v>
       </c>
       <c r="B31" t="n">
-        <v>91925</v>
+        <v>91927</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -4097,7 +4097,7 @@
         <v>128944579</v>
       </c>
       <c r="B31" t="n">
-        <v>91927</v>
+        <v>91931</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -4097,7 +4097,7 @@
         <v>128944579</v>
       </c>
       <c r="B31" t="n">
-        <v>91931</v>
+        <v>91932</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118525987</v>
+        <v>118658795</v>
       </c>
       <c r="B2" t="n">
-        <v>91133</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,30 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585152</v>
+        <v>585109</v>
       </c>
       <c r="R2" t="n">
-        <v>6558846</v>
+        <v>6558533</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +752,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Vid roten på gammal granlåga. Rikligt med torrgranar som angripits av granbarkborrar. Gott om granlågor av både gamla rötskadade och färska torrgranar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,33 +771,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Olsson, Björn Rösch</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118526068</v>
+        <v>118659096</v>
       </c>
       <c r="B3" t="n">
-        <v>8416</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,36 +801,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585130</v>
+        <v>585101</v>
       </c>
       <c r="R3" t="n">
-        <v>6558822</v>
+        <v>6558610</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +867,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:02</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:02</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På kraftigt rötangripen granstubbe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,68 +886,65 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Olsson, Björn Rösch</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118659661</v>
+        <v>118659613</v>
       </c>
       <c r="B4" t="n">
-        <v>89966</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2008</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -970,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585347</v>
+        <v>585340</v>
       </c>
       <c r="R4" t="n">
-        <v>6558564</v>
+        <v>6558598</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1010,7 +992,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>8 fjolårsexemplar i barrmatta under gammal gran.</t>
+          <t>Vid roten på gammal kraftigt rötskadad granlåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,15 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118658920</v>
+        <v>121236892</v>
       </c>
       <c r="B5" t="n">
-        <v>104952</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,38 +1031,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lovisetorp, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585085</v>
+        <v>585209</v>
       </c>
       <c r="R5" t="n">
-        <v>6558588</v>
+        <v>6558799</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,17 +1094,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Liten lokal med en blommande stjälk.</t>
+          <t>3 nya/färska kapslar. I basen/På rotbenet av gammal, rötad granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,34 +1113,32 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Björn Rösch, Rolf Olsson, Bo Karlsson, Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Häradskog - Second opinion Hälleforsnäs</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118659096</v>
+        <v>121236904</v>
       </c>
       <c r="B6" t="n">
-        <v>94478</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,7 +1165,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1193,19 +1173,16 @@
           <t>kapslar</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lovisetorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585101</v>
+        <v>585098</v>
       </c>
       <c r="R6" t="n">
-        <v>6558610</v>
+        <v>6558618</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1232,17 +1209,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På kraftigt rötangripen granstubbe.</t>
+          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,34 +1228,32 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson, Rolf Olsson, Björn Rösch</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Häradskog - Second opinion Hälleforsnäs</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>118659200</v>
       </c>
       <c r="B7" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,53 +1356,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118659444</v>
+        <v>121236906</v>
       </c>
       <c r="B8" t="n">
-        <v>91133</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lovisetorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585230</v>
+        <v>585120</v>
       </c>
       <c r="R8" t="n">
-        <v>6558800</v>
+        <v>6558607</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1454,17 +1430,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På högstubbe av gran.</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,84 +1444,79 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson, Rolf Olsson, Björn Rösch</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Häradskog - Second opinion Hälleforsnäs</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118659613</v>
+        <v>121236903</v>
       </c>
       <c r="B9" t="n">
-        <v>94478</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lovisetorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585340</v>
+        <v>585174</v>
       </c>
       <c r="R9" t="n">
-        <v>6558598</v>
+        <v>6558553</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,17 +1540,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Vid roten på gammal kraftigt rötskadad granlåga.</t>
+          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,34 +1559,32 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson, Rolf Olsson, Björn Rösch</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Häradskog - Second opinion Hälleforsnäs</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118658795</v>
+        <v>118525987</v>
       </c>
       <c r="B10" t="n">
-        <v>94478</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1628,35 +1592,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>210</v>
+        <v>1339</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1664,13 +1623,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585109</v>
+        <v>585152</v>
       </c>
       <c r="R10" t="n">
-        <v>6558533</v>
+        <v>6558846</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1694,17 +1653,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Vid roten på gammal granlåga. Rikligt med torrgranar som angripits av granbarkborrar. Gott om granlågor av både gamla rötskadade och färska torrgranar.</t>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,34 +1677,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Björn Rösch, Rolf Olsson, Bo Karlsson, Bo Törnquist</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118659687</v>
+        <v>118526311</v>
       </c>
       <c r="B11" t="n">
-        <v>89963</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,28 +1706,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4189</v>
+        <v>1339</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1783,13 +1737,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585362</v>
+        <v>585159</v>
       </c>
       <c r="R11" t="n">
-        <v>6558555</v>
+        <v>6558684</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1813,17 +1767,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Fjolårsexemplar i barrmatta under gammal gran.</t>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,34 +1791,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson, Rolf Olsson, Björn Rösch</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118659699</v>
+        <v>118659444</v>
       </c>
       <c r="B12" t="n">
-        <v>89963</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,33 +1820,25 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4189</v>
+        <v>1339</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1902,10 +1847,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585361</v>
+        <v>585230</v>
       </c>
       <c r="R12" t="n">
-        <v>6558542</v>
+        <v>6558800</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1940,6 +1885,11 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På högstubbe av gran.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1958,80 +1908,58 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Björn Rösch, Rolf Olsson, Bo Karlsson, Bo Törnquist</t>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Olsson, Björn Rösch</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118714058</v>
+        <v>128944579</v>
       </c>
       <c r="B13" t="n">
-        <v>108726</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>1506</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Hälleforsnäs IP, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585141</v>
+        <v>585270</v>
       </c>
       <c r="R13" t="n">
-        <v>6558752</v>
+        <v>6558560</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2053,19 +1981,14 @@
           <t>Mellösa</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>D-Fle-0206</t>
-        </is>
-      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2078,44 +2001,40 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Öppen fastmark - med eller utan enstaka träd</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>I vägslänt</t>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Rolf Olsson, Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120265464</v>
+        <v>118659661</v>
       </c>
       <c r="B14" t="n">
-        <v>91990</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>91333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2123,26 +2042,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>2008</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2158,13 +2077,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585302</v>
+        <v>585347</v>
       </c>
       <c r="R14" t="n">
-        <v>6558523</v>
+        <v>6558564</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2188,27 +2107,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:08</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Växer under ett bestånd med tall på hällmark.</t>
+          <t>8 fjolårsexemplar i barrmatta under gammal gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2217,80 +2126,79 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Olsson, Björn Rösch</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121236902</v>
+        <v>121236894</v>
       </c>
       <c r="B15" t="n">
-        <v>92031</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585294</v>
+        <v>585209</v>
       </c>
       <c r="R15" t="n">
-        <v>6558517</v>
+        <v>6558636</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2328,6 +2236,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2350,57 +2259,59 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121236898</v>
+        <v>118659687</v>
       </c>
       <c r="B16" t="n">
-        <v>57509</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>4189</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lovisetorp, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585384</v>
+        <v>585362</v>
       </c>
       <c r="R16" t="n">
-        <v>6558510</v>
+        <v>6558555</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2424,12 +2335,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fjolårsexemplar i barrmatta under gammal gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2438,84 +2354,78 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Häradskog - Second opinion Hälleforsnäs</t>
-        </is>
-      </c>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Olsson, Björn Rösch</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121236903</v>
+        <v>118659699</v>
       </c>
       <c r="B17" t="n">
-        <v>91160</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>4189</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lovisetorp, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585174</v>
+        <v>585361</v>
       </c>
       <c r="R17" t="n">
-        <v>6558553</v>
+        <v>6558542</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2539,17 +2449,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Vid inventeringstillfället en ung fruktkropp på ca 20cm grov granlåga.</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2558,64 +2463,56 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Häradskog - Second opinion Hälleforsnäs</t>
-        </is>
-      </c>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Olsson, Björn Rösch</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121236896</v>
+        <v>121236899</v>
       </c>
       <c r="B18" t="n">
-        <v>92031</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>4189</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2629,13 +2526,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585454</v>
+        <v>585358</v>
       </c>
       <c r="R18" t="n">
-        <v>6558597</v>
+        <v>6558558</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2695,62 +2592,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121236901</v>
+        <v>121236893</v>
       </c>
       <c r="B19" t="n">
-        <v>94723</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>210</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lundtorp, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585340</v>
+        <v>585245</v>
       </c>
       <c r="R19" t="n">
-        <v>6558597</v>
+        <v>6558734</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2780,11 +2672,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>1 äldre kapsel.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2815,59 +2702,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121236904</v>
+        <v>128944644</v>
       </c>
       <c r="B20" t="n">
-        <v>94723</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91424</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>210</v>
+        <v>5733</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Vent.) Schild</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Hälleforsnäs IP, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585098</v>
+        <v>585252</v>
       </c>
       <c r="R20" t="n">
-        <v>6558618</v>
+        <v>6558691</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2894,17 +2770,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Flera gamla (fjolårets) samt några nybildade kapslar.</t>
+          <t>Gelatinös, gulfärgad fingersvamp. Abortiva smågrenar vid basen. Växte i barrblandskog, någon enstaka ek fanns även i närheten.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2913,13 +2789,14 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -2927,45 +2804,36 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Häradskog - Second opinion Hälleforsnäs</t>
-        </is>
-      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121236892</v>
+        <v>120265464</v>
       </c>
       <c r="B21" t="n">
-        <v>94723</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>210</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2975,22 +2843,24 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Lovisetorp, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585209</v>
+        <v>585302</v>
       </c>
       <c r="R21" t="n">
-        <v>6558799</v>
+        <v>6558523</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3014,17 +2884,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>3 nya/färska kapslar. I basen/På rotbenet av gammal, rötad granlåga</t>
+          <t>Växer under ett bestånd med tall på hällmark.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3039,31 +2919,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Häradskog - Second opinion Hälleforsnäs</t>
-        </is>
-      </c>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121236891</v>
+        <v>120267932</v>
       </c>
       <c r="B22" t="n">
-        <v>55958</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3071,21 +2942,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>206004</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3093,23 +2964,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Lovisetorp, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585154</v>
+        <v>585475</v>
       </c>
       <c r="R22" t="n">
-        <v>6558832</v>
+        <v>6558602</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3133,12 +3007,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Växer på hällmark i barrblandskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3153,31 +3042,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Häradskog - Second opinion Hälleforsnäs</t>
-        </is>
-      </c>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121236906</v>
+        <v>121236896</v>
       </c>
       <c r="B23" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3185,26 +3065,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3218,10 +3098,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585120</v>
+        <v>585454</v>
       </c>
       <c r="R23" t="n">
-        <v>6558607</v>
+        <v>6558597</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3284,42 +3164,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121236893</v>
+        <v>121236902</v>
       </c>
       <c r="B24" t="n">
-        <v>91996</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3329,17 +3204,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lundtorp, Srm</t>
+          <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585245</v>
+        <v>585294</v>
       </c>
       <c r="R24" t="n">
-        <v>6558734</v>
+        <v>6558517</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3399,15 +3274,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121236895</v>
+        <v>121236908</v>
       </c>
       <c r="B25" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3415,31 +3285,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3448,13 +3318,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585246</v>
+        <v>585051</v>
       </c>
       <c r="R25" t="n">
-        <v>6558647</v>
+        <v>6558550</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3484,11 +3354,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Hackspår i basen av murket barrträd</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3519,15 +3384,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121236894</v>
+        <v>121236895</v>
       </c>
       <c r="B26" t="n">
-        <v>94877</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3535,46 +3395,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bruksdammen, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585209</v>
+        <v>585246</v>
       </c>
       <c r="R26" t="n">
-        <v>6558636</v>
+        <v>6558647</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3609,13 +3466,17 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Hackspår i basen av murket barrträd</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3638,62 +3499,60 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121236907</v>
+        <v>120266943</v>
       </c>
       <c r="B27" t="n">
-        <v>92024</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56845</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5449</v>
+        <v>100053</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lovisetorp, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585060</v>
+        <v>585465</v>
       </c>
       <c r="R27" t="n">
-        <v>6558591</v>
+        <v>6558619</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3717,12 +3576,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3737,63 +3606,50 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Häradskog - Second opinion Hälleforsnäs</t>
-        </is>
-      </c>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121236908</v>
+        <v>121236905</v>
       </c>
       <c r="B28" t="n">
-        <v>92031</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3802,13 +3658,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585051</v>
+        <v>585113</v>
       </c>
       <c r="R28" t="n">
-        <v>6558550</v>
+        <v>6558608</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3868,62 +3724,64 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121236899</v>
+        <v>120267180</v>
       </c>
       <c r="B29" t="n">
-        <v>90151</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4189</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bruksdammen, Srm</t>
+          <t>Lovisetorp, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585358</v>
+        <v>585473</v>
       </c>
       <c r="R29" t="n">
-        <v>6558558</v>
+        <v>6558609</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3947,12 +3805,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3967,59 +3835,49 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Häradskog - Second opinion Hälleforsnäs</t>
-        </is>
-      </c>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121236905</v>
+        <v>121236898</v>
       </c>
       <c r="B30" t="n">
-        <v>5172</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4028,10 +3886,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585113</v>
+        <v>585384</v>
       </c>
       <c r="R30" t="n">
-        <v>6558608</v>
+        <v>6558510</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4094,51 +3952,61 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128944579</v>
+        <v>118526068</v>
       </c>
       <c r="B31" t="n">
-        <v>91932</v>
+        <v>8455</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1506</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hälleforsnäs IP, Srm</t>
+          <t>Lovisetorp, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585270</v>
+        <v>585130</v>
       </c>
       <c r="R31" t="n">
-        <v>6558560</v>
+        <v>6558822</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4162,12 +4030,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4176,37 +4054,374 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>121236891</v>
+      </c>
+      <c r="B32" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lundtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>585154</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6558832</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Häradskog - Second opinion Hälleforsnäs</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>118714058</v>
+      </c>
+      <c r="B33" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lundtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>585141</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6558752</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D-Fle-0206</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Öppen fastmark - med eller utan enstaka träd</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>I vägslänt</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Bo Karlsson, Rolf Olsson, Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>118658920</v>
+      </c>
+      <c r="B34" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lovisetorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>585085</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6558588</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Liten lokal med en blommande stjälk.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Olsson, Björn Rösch</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28433-2024 artfynd.xlsx
+++ b/artfynd/A 28433-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118658795</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118659096</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118659613</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
           <t>Häradskog - Second opinion Hälleforsnäs</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121236892</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1245,6 +1270,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Häradskog - Second opinion Hälleforsnäs</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121236904</t>
         </is>
       </c>
     </row>
@@ -1353,6 +1383,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118659200</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1463,6 +1498,11 @@
           <t>Häradskog - Second opinion Hälleforsnäs</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121236906</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1578,6 +1618,11 @@
           <t>Häradskog - Second opinion Hälleforsnäs</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121236903</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1692,6 +1737,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118525987</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1806,6 +1856,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118526311</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1912,6 +1967,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118659444</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2028,6 +2088,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128944579</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2142,6 +2207,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118659661</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2256,6 +2326,11 @@
           <t>Häradskog - Second opinion Hälleforsnäs</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121236894</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2370,6 +2445,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118659687</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2479,6 +2559,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118659699</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2589,6 +2674,11 @@
           <t>Häradskog - Second opinion Hälleforsnäs</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121236899</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2697,6 +2787,11 @@
       <c r="AY19" t="inlineStr">
         <is>
           <t>Häradskog - Second opinion Hälleforsnäs</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121236893</t>
         </is>
       </c>
     </row>
@@ -2805,6 +2900,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128944644</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2928,6 +3028,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120265464</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3051,6 +3156,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120267932</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3161,6 +3271,11 @@
           <t>Häradskog - Second opinion Hälleforsnäs</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121236896</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3271,6 +3386,11 @@
           <t>Häradskog - Second opinion Hälleforsnäs</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121236902</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3381,6 +3501,11 @@
           <t>Häradskog - Second opinion Hälleforsnäs</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121236908</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3496,6 +3621,11 @@
           <t>Häradskog - Second opinion Hälleforsnäs</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121236895</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3615,6 +3745,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120266943</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3721,6 +3856,11 @@
           <t>Häradskog - Second opinion Hälleforsnäs</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121236905</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3844,6 +3984,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120267180</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3949,6 +4094,11 @@
           <t>Häradskog - Second opinion Hälleforsnäs</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121236898</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4069,6 +4219,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118526068</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4178,6 +4333,11 @@
           <t>Häradskog - Second opinion Hälleforsnäs</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121236891</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4313,6 +4473,11 @@
       <c r="AY33" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118714058</t>
         </is>
       </c>
     </row>
@@ -4422,8 +4587,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118658920</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>